--- a/data/nzd0114/nzd0114.xlsx
+++ b/data/nzd0114/nzd0114.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN203"/>
+  <dimension ref="A1:AN204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25797,6 +25797,128 @@
         </is>
       </c>
     </row>
+    <row r="204">
+      <c r="A204" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:05:44+00:00</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>279.67</v>
+      </c>
+      <c r="C204" t="n">
+        <v>280.55</v>
+      </c>
+      <c r="D204" t="n">
+        <v>283.45</v>
+      </c>
+      <c r="E204" t="n">
+        <v>285.77</v>
+      </c>
+      <c r="F204" t="n">
+        <v>289.92</v>
+      </c>
+      <c r="G204" t="n">
+        <v>279.82</v>
+      </c>
+      <c r="H204" t="n">
+        <v>276.55</v>
+      </c>
+      <c r="I204" t="n">
+        <v>274.96</v>
+      </c>
+      <c r="J204" t="n">
+        <v>274.84</v>
+      </c>
+      <c r="K204" t="n">
+        <v>279.98</v>
+      </c>
+      <c r="L204" t="n">
+        <v>296.9</v>
+      </c>
+      <c r="M204" t="n">
+        <v>310.74</v>
+      </c>
+      <c r="N204" t="n">
+        <v>316.12</v>
+      </c>
+      <c r="O204" t="n">
+        <v>324.08</v>
+      </c>
+      <c r="P204" t="n">
+        <v>313.49</v>
+      </c>
+      <c r="Q204" t="n">
+        <v>311.28</v>
+      </c>
+      <c r="R204" t="n">
+        <v>306.55</v>
+      </c>
+      <c r="S204" t="n">
+        <v>311.2</v>
+      </c>
+      <c r="T204" t="n">
+        <v>317.2</v>
+      </c>
+      <c r="U204" t="n">
+        <v>321.24</v>
+      </c>
+      <c r="V204" t="n">
+        <v>331.21</v>
+      </c>
+      <c r="W204" t="n">
+        <v>324.28</v>
+      </c>
+      <c r="X204" t="n">
+        <v>346.77</v>
+      </c>
+      <c r="Y204" t="n">
+        <v>351.07</v>
+      </c>
+      <c r="Z204" t="n">
+        <v>337.59</v>
+      </c>
+      <c r="AA204" t="n">
+        <v>333.4</v>
+      </c>
+      <c r="AB204" t="n">
+        <v>331.47</v>
+      </c>
+      <c r="AC204" t="n">
+        <v>328.21</v>
+      </c>
+      <c r="AD204" t="n">
+        <v>315.88</v>
+      </c>
+      <c r="AE204" t="n">
+        <v>312.98</v>
+      </c>
+      <c r="AF204" t="n">
+        <v>298</v>
+      </c>
+      <c r="AG204" t="n">
+        <v>290.23</v>
+      </c>
+      <c r="AH204" t="n">
+        <v>274.29</v>
+      </c>
+      <c r="AI204" t="n">
+        <v>275.85</v>
+      </c>
+      <c r="AJ204" t="n">
+        <v>275.59</v>
+      </c>
+      <c r="AK204" t="inlineStr"/>
+      <c r="AL204" t="n">
+        <v>258.38</v>
+      </c>
+      <c r="AM204" t="inlineStr"/>
+      <c r="AN204" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -25808,7 +25930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B206"/>
+  <dimension ref="A1:B207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27871,6 +27993,16 @@
       </c>
       <c r="B206" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>0.49</v>
       </c>
     </row>
   </sheetData>
@@ -28039,28 +28171,28 @@
         <v>0.0582</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2579191478366459</v>
+        <v>0.2517771342004353</v>
       </c>
       <c r="J2" t="n">
+        <v>203</v>
+      </c>
+      <c r="K2" t="n">
         <v>202</v>
       </c>
-      <c r="K2" t="n">
-        <v>201</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.02584939435953526</v>
+        <v>0.02487710330816029</v>
       </c>
       <c r="M2" t="n">
-        <v>9.629699598242679</v>
+        <v>9.610358766989165</v>
       </c>
       <c r="N2" t="n">
-        <v>130.8971055969623</v>
+        <v>130.4398199390647</v>
       </c>
       <c r="O2" t="n">
-        <v>11.44102729639967</v>
+        <v>11.42102534534727</v>
       </c>
       <c r="P2" t="n">
-        <v>279.1398926556587</v>
+        <v>279.2065387294568</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -28117,28 +28249,28 @@
         <v>0.0562</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3860514511150044</v>
+        <v>0.3832935562952899</v>
       </c>
       <c r="J3" t="n">
+        <v>203</v>
+      </c>
+      <c r="K3" t="n">
         <v>202</v>
       </c>
-      <c r="K3" t="n">
-        <v>201</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.04543911706792669</v>
+        <v>0.0452553308895276</v>
       </c>
       <c r="M3" t="n">
-        <v>10.71752438924092</v>
+        <v>10.67936833967052</v>
       </c>
       <c r="N3" t="n">
-        <v>163.4749707528808</v>
+        <v>162.7041416694421</v>
       </c>
       <c r="O3" t="n">
-        <v>12.78573309407329</v>
+        <v>12.75555336586548</v>
       </c>
       <c r="P3" t="n">
-        <v>273.2032272771853</v>
+        <v>273.2331527824949</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -28195,28 +28327,28 @@
         <v>0.0536</v>
       </c>
       <c r="I4" t="n">
-        <v>0.336599354243807</v>
+        <v>0.3357678885646431</v>
       </c>
       <c r="J4" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K4" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03379123079590474</v>
+        <v>0.03396595007975267</v>
       </c>
       <c r="M4" t="n">
-        <v>10.86253984060468</v>
+        <v>10.81286229269379</v>
       </c>
       <c r="N4" t="n">
-        <v>169.6601911090283</v>
+        <v>168.8196243839638</v>
       </c>
       <c r="O4" t="n">
-        <v>13.02536721589946</v>
+        <v>12.99306062419335</v>
       </c>
       <c r="P4" t="n">
-        <v>275.4391846934521</v>
+        <v>275.448204252591</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -28273,28 +28405,28 @@
         <v>0.0601</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2548824988730224</v>
+        <v>0.2514396124712802</v>
       </c>
       <c r="J5" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K5" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01922962628304448</v>
+        <v>0.01890880616787138</v>
       </c>
       <c r="M5" t="n">
-        <v>10.93546824706069</v>
+        <v>10.89938454734707</v>
       </c>
       <c r="N5" t="n">
-        <v>170.4207588104773</v>
+        <v>169.6315614326128</v>
       </c>
       <c r="O5" t="n">
-        <v>13.05453020259547</v>
+        <v>13.02426817263115</v>
       </c>
       <c r="P5" t="n">
-        <v>282.5223860387983</v>
+        <v>282.5601317128724</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -28351,28 +28483,28 @@
         <v>0.0604</v>
       </c>
       <c r="I6" t="n">
-        <v>0.06638215947060505</v>
+        <v>0.06431105297154326</v>
       </c>
       <c r="J6" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K6" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001250651555609883</v>
+        <v>0.001185974948622603</v>
       </c>
       <c r="M6" t="n">
-        <v>11.42835786482528</v>
+        <v>11.38210962444475</v>
       </c>
       <c r="N6" t="n">
-        <v>181.3792835352039</v>
+        <v>180.4891985583007</v>
       </c>
       <c r="O6" t="n">
-        <v>13.46771263189128</v>
+        <v>13.43462684849493</v>
       </c>
       <c r="P6" t="n">
-        <v>290.2551857029429</v>
+        <v>290.2779393144054</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -28429,28 +28561,28 @@
         <v>0.0414</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3232100981669145</v>
+        <v>0.3119063664218869</v>
       </c>
       <c r="J7" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K7" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0207390012896741</v>
+        <v>0.01949338992259042</v>
       </c>
       <c r="M7" t="n">
-        <v>13.44076677643871</v>
+        <v>13.43392992904797</v>
       </c>
       <c r="N7" t="n">
-        <v>248.8723537025586</v>
+        <v>248.2375322658199</v>
       </c>
       <c r="O7" t="n">
-        <v>15.77568869186251</v>
+        <v>15.75555560003581</v>
       </c>
       <c r="P7" t="n">
-        <v>282.4772876598738</v>
+        <v>282.6029525674737</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -28507,28 +28639,28 @@
         <v>0.0535</v>
       </c>
       <c r="I8" t="n">
-        <v>0.215659788681187</v>
+        <v>0.2054887796477338</v>
       </c>
       <c r="J8" t="n">
+        <v>203</v>
+      </c>
+      <c r="K8" t="n">
         <v>202</v>
       </c>
-      <c r="K8" t="n">
-        <v>201</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.009384826780154398</v>
+        <v>0.00859906019300416</v>
       </c>
       <c r="M8" t="n">
-        <v>13.06966097763467</v>
+        <v>13.05891762594158</v>
       </c>
       <c r="N8" t="n">
-        <v>252.0305508865642</v>
+        <v>251.2927608377186</v>
       </c>
       <c r="O8" t="n">
-        <v>15.87547009970301</v>
+        <v>15.85221627526317</v>
       </c>
       <c r="P8" t="n">
-        <v>281.1074362918786</v>
+        <v>281.2188873540921</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -28585,28 +28717,28 @@
         <v>0.0598</v>
       </c>
       <c r="I9" t="n">
-        <v>0.07241598573089575</v>
+        <v>0.06264580150177057</v>
       </c>
       <c r="J9" t="n">
+        <v>203</v>
+      </c>
+      <c r="K9" t="n">
         <v>202</v>
       </c>
-      <c r="K9" t="n">
-        <v>201</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.001542473395100274</v>
+        <v>0.001163711424088887</v>
       </c>
       <c r="M9" t="n">
-        <v>11.05239381460332</v>
+        <v>11.04052881558215</v>
       </c>
       <c r="N9" t="n">
-        <v>174.2677122612856</v>
+        <v>173.875490890328</v>
       </c>
       <c r="O9" t="n">
-        <v>13.20104966513215</v>
+        <v>13.18618560806452</v>
       </c>
       <c r="P9" t="n">
-        <v>282.8791349695045</v>
+        <v>282.9861939060148</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -28663,28 +28795,28 @@
         <v>0.0436</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1575269256111534</v>
+        <v>-0.167169500808194</v>
       </c>
       <c r="J10" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K10" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L10" t="n">
-        <v>0.006896866611028285</v>
+        <v>0.007822407034739243</v>
       </c>
       <c r="M10" t="n">
-        <v>11.03671712386527</v>
+        <v>11.02818794682824</v>
       </c>
       <c r="N10" t="n">
-        <v>179.8246822592392</v>
+        <v>179.3750474965777</v>
       </c>
       <c r="O10" t="n">
-        <v>13.40987256685309</v>
+        <v>13.3930970091528</v>
       </c>
       <c r="P10" t="n">
-        <v>288.5150959639892</v>
+        <v>288.6221003648029</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -28741,28 +28873,28 @@
         <v>0.057</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.01287452465136611</v>
+        <v>-0.02091541175344186</v>
       </c>
       <c r="J11" t="n">
+        <v>203</v>
+      </c>
+      <c r="K11" t="n">
         <v>202</v>
       </c>
-      <c r="K11" t="n">
-        <v>201</v>
-      </c>
       <c r="L11" t="n">
-        <v>4.669326630935e-05</v>
+        <v>0.0001242948119333231</v>
       </c>
       <c r="M11" t="n">
-        <v>11.39201909337362</v>
+        <v>11.37417771494022</v>
       </c>
       <c r="N11" t="n">
-        <v>182.2317289306994</v>
+        <v>181.6482702511477</v>
       </c>
       <c r="O11" t="n">
-        <v>13.49932327676833</v>
+        <v>13.47769528707144</v>
       </c>
       <c r="P11" t="n">
-        <v>288.4038924281637</v>
+        <v>288.4920022121308</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -28819,28 +28951,28 @@
         <v>0.0868</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.0004122611996159854</v>
+        <v>0.0004285480097116548</v>
       </c>
       <c r="J12" t="n">
+        <v>203</v>
+      </c>
+      <c r="K12" t="n">
         <v>202</v>
       </c>
-      <c r="K12" t="n">
-        <v>201</v>
-      </c>
       <c r="L12" t="n">
-        <v>3.901877909662232e-08</v>
+        <v>4.260352315377247e-08</v>
       </c>
       <c r="M12" t="n">
-        <v>12.64440639763281</v>
+        <v>12.58583311098151</v>
       </c>
       <c r="N12" t="n">
-        <v>223.6183080792545</v>
+        <v>222.5147712474127</v>
       </c>
       <c r="O12" t="n">
-        <v>14.95387267831495</v>
+        <v>14.91692901529711</v>
       </c>
       <c r="P12" t="n">
-        <v>296.0620658752841</v>
+        <v>296.0528525239646</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -28897,28 +29029,28 @@
         <v>0.0509</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.03748784629534286</v>
+        <v>-0.0358495564344643</v>
       </c>
       <c r="J13" t="n">
+        <v>203</v>
+      </c>
+      <c r="K13" t="n">
         <v>202</v>
       </c>
-      <c r="K13" t="n">
-        <v>201</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.0002697740350466882</v>
+        <v>0.00024928643546962</v>
       </c>
       <c r="M13" t="n">
-        <v>13.26238330289743</v>
+        <v>13.20542216938256</v>
       </c>
       <c r="N13" t="n">
-        <v>267.3620605092194</v>
+        <v>266.0517149349351</v>
       </c>
       <c r="O13" t="n">
-        <v>16.35120975674948</v>
+        <v>16.31109177630164</v>
       </c>
       <c r="P13" t="n">
-        <v>310.0788045362875</v>
+        <v>310.0608526158234</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -28975,28 +29107,28 @@
         <v>0.0503</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.01683768092916892</v>
+        <v>-0.02537552612876463</v>
       </c>
       <c r="J14" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K14" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L14" t="n">
-        <v>6.218321642881275e-05</v>
+        <v>0.0001424736916942893</v>
       </c>
       <c r="M14" t="n">
-        <v>12.33913251151504</v>
+        <v>12.31192822292957</v>
       </c>
       <c r="N14" t="n">
-        <v>234.9333717743076</v>
+        <v>234.1210235190603</v>
       </c>
       <c r="O14" t="n">
-        <v>15.32753638959333</v>
+        <v>15.30101380690379</v>
       </c>
       <c r="P14" t="n">
-        <v>325.1362051162872</v>
+        <v>325.2298532941687</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -29053,28 +29185,28 @@
         <v>0.0624</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.09053337774201277</v>
+        <v>-0.08876017503908699</v>
       </c>
       <c r="J15" t="n">
+        <v>203</v>
+      </c>
+      <c r="K15" t="n">
         <v>202</v>
       </c>
-      <c r="K15" t="n">
-        <v>201</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.002073888909202126</v>
+        <v>0.002014287587355557</v>
       </c>
       <c r="M15" t="n">
-        <v>11.56597147075607</v>
+        <v>11.51976988275669</v>
       </c>
       <c r="N15" t="n">
-        <v>202.4726972473541</v>
+        <v>201.4858546650232</v>
       </c>
       <c r="O15" t="n">
-        <v>14.22929011747789</v>
+        <v>14.19457130966001</v>
       </c>
       <c r="P15" t="n">
-        <v>324.6751914973536</v>
+        <v>324.6557612398333</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -29131,28 +29263,28 @@
         <v>0.0615</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.08708729691462568</v>
+        <v>-0.08744786018344995</v>
       </c>
       <c r="J16" t="n">
+        <v>203</v>
+      </c>
+      <c r="K16" t="n">
         <v>202</v>
       </c>
-      <c r="K16" t="n">
-        <v>201</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.002065562150822431</v>
+        <v>0.002104423888428242</v>
       </c>
       <c r="M16" t="n">
-        <v>11.23321675382824</v>
+        <v>11.1792139536059</v>
       </c>
       <c r="N16" t="n">
-        <v>188.1089624106063</v>
+        <v>187.1783707019169</v>
       </c>
       <c r="O16" t="n">
-        <v>13.71528207550272</v>
+        <v>13.68131465546776</v>
       </c>
       <c r="P16" t="n">
-        <v>316.140072972882</v>
+        <v>316.1440239239797</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -29209,28 +29341,28 @@
         <v>0.0573</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.253600312252549</v>
+        <v>-0.2511898395142058</v>
       </c>
       <c r="J17" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K17" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0145227480275324</v>
+        <v>0.01439685811534863</v>
       </c>
       <c r="M17" t="n">
-        <v>12.41410706450877</v>
+        <v>12.36629532204194</v>
       </c>
       <c r="N17" t="n">
-        <v>224.2714386725006</v>
+        <v>223.1843891836421</v>
       </c>
       <c r="O17" t="n">
-        <v>14.97569493120438</v>
+        <v>14.93935705389098</v>
       </c>
       <c r="P17" t="n">
-        <v>315.5294532974848</v>
+        <v>315.5030116606511</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -29287,28 +29419,28 @@
         <v>0.0537</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1476688897498672</v>
+        <v>-0.1489299329453465</v>
       </c>
       <c r="J18" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K18" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L18" t="n">
-        <v>0.005076227780501541</v>
+        <v>0.005216209382864712</v>
       </c>
       <c r="M18" t="n">
-        <v>12.25844349927735</v>
+        <v>12.2021762697172</v>
       </c>
       <c r="N18" t="n">
-        <v>219.887961580611</v>
+        <v>218.7964108339274</v>
       </c>
       <c r="O18" t="n">
-        <v>14.82861967887136</v>
+        <v>14.79176834708844</v>
       </c>
       <c r="P18" t="n">
-        <v>311.7002799371991</v>
+        <v>311.7141265432215</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -29365,28 +29497,28 @@
         <v>0.0545</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.03934872778681087</v>
+        <v>-0.03811589016516204</v>
       </c>
       <c r="J19" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K19" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0003175730067314086</v>
+        <v>0.0003011316028920241</v>
       </c>
       <c r="M19" t="n">
-        <v>12.87431254697631</v>
+        <v>12.81760570607729</v>
       </c>
       <c r="N19" t="n">
-        <v>245.2884221621465</v>
+        <v>244.0753562128295</v>
       </c>
       <c r="O19" t="n">
-        <v>15.66168644055124</v>
+        <v>15.62291125919972</v>
       </c>
       <c r="P19" t="n">
-        <v>311.0164672607085</v>
+        <v>311.0027863665168</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -29443,28 +29575,28 @@
         <v>0.0533</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.03458640007763745</v>
+        <v>-0.03078616374370053</v>
       </c>
       <c r="J20" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K20" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0002375524511197824</v>
+        <v>0.0001901724858339726</v>
       </c>
       <c r="M20" t="n">
-        <v>12.86795068614045</v>
+        <v>12.82510862095011</v>
       </c>
       <c r="N20" t="n">
-        <v>257.535739916646</v>
+        <v>256.3244532658518</v>
       </c>
       <c r="O20" t="n">
-        <v>16.04792011186017</v>
+        <v>16.01013595400901</v>
       </c>
       <c r="P20" t="n">
-        <v>314.3265865847425</v>
+        <v>314.2849303571303</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -29521,28 +29653,28 @@
         <v>0.0487</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1516892134218073</v>
+        <v>-0.1489622310377812</v>
       </c>
       <c r="J21" t="n">
+        <v>203</v>
+      </c>
+      <c r="K21" t="n">
         <v>202</v>
       </c>
-      <c r="K21" t="n">
-        <v>201</v>
-      </c>
       <c r="L21" t="n">
-        <v>0.004921738420377686</v>
+        <v>0.004796087123760784</v>
       </c>
       <c r="M21" t="n">
-        <v>12.48028999346576</v>
+        <v>12.43469510626394</v>
       </c>
       <c r="N21" t="n">
-        <v>237.8145231506539</v>
+        <v>236.6736174944722</v>
       </c>
       <c r="O21" t="n">
-        <v>15.42123610968505</v>
+        <v>15.38420025527724</v>
       </c>
       <c r="P21" t="n">
-        <v>322.4978728580798</v>
+        <v>322.4679240204202</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -29599,28 +29731,28 @@
         <v>0.0493</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2568792366543611</v>
+        <v>-0.2504636431590707</v>
       </c>
       <c r="J22" t="n">
+        <v>203</v>
+      </c>
+      <c r="K22" t="n">
         <v>202</v>
       </c>
-      <c r="K22" t="n">
-        <v>201</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.0132179484886269</v>
+        <v>0.01269446318152789</v>
       </c>
       <c r="M22" t="n">
-        <v>12.66886798365308</v>
+        <v>12.64251294272251</v>
       </c>
       <c r="N22" t="n">
-        <v>251.8288338484189</v>
+        <v>250.7835930452864</v>
       </c>
       <c r="O22" t="n">
-        <v>15.86911572358142</v>
+        <v>15.83614830207416</v>
       </c>
       <c r="P22" t="n">
-        <v>331.5423827179005</v>
+        <v>331.4719240419641</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -29677,28 +29809,28 @@
         <v>0.0539</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.4599070809190898</v>
+        <v>-0.4668504847306611</v>
       </c>
       <c r="J23" t="n">
+        <v>203</v>
+      </c>
+      <c r="K23" t="n">
         <v>202</v>
       </c>
-      <c r="K23" t="n">
-        <v>201</v>
-      </c>
       <c r="L23" t="n">
-        <v>0.04230151362553136</v>
+        <v>0.04392885003112301</v>
       </c>
       <c r="M23" t="n">
-        <v>12.75202594179116</v>
+        <v>12.71964640014589</v>
       </c>
       <c r="N23" t="n">
-        <v>244.7954547745985</v>
+        <v>243.8195404124703</v>
       </c>
       <c r="O23" t="n">
-        <v>15.64594052061424</v>
+        <v>15.61472191274857</v>
       </c>
       <c r="P23" t="n">
-        <v>343.3400582791858</v>
+        <v>343.416313584235</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -29755,28 +29887,28 @@
         <v>0.0592</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.4088686527153621</v>
+        <v>-0.4049870899239543</v>
       </c>
       <c r="J24" t="n">
+        <v>203</v>
+      </c>
+      <c r="K24" t="n">
         <v>202</v>
       </c>
-      <c r="K24" t="n">
-        <v>201</v>
-      </c>
       <c r="L24" t="n">
-        <v>0.03351195267629037</v>
+        <v>0.03322391940073421</v>
       </c>
       <c r="M24" t="n">
-        <v>12.74306011638677</v>
+        <v>12.70027060501256</v>
       </c>
       <c r="N24" t="n">
-        <v>246.4646554764823</v>
+        <v>245.318269138921</v>
       </c>
       <c r="O24" t="n">
-        <v>15.69919282882029</v>
+        <v>15.66263927755859</v>
       </c>
       <c r="P24" t="n">
-        <v>353.6328599652766</v>
+        <v>353.590231052605</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -29833,28 +29965,28 @@
         <v>0.0698</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3168602309161194</v>
+        <v>-0.3228865846402686</v>
       </c>
       <c r="J25" t="n">
+        <v>203</v>
+      </c>
+      <c r="K25" t="n">
         <v>202</v>
       </c>
-      <c r="K25" t="n">
-        <v>201</v>
-      </c>
       <c r="L25" t="n">
-        <v>0.02309917714366705</v>
+        <v>0.02419110213579667</v>
       </c>
       <c r="M25" t="n">
-        <v>11.97527140888699</v>
+        <v>11.94353142266918</v>
       </c>
       <c r="N25" t="n">
-        <v>217.059950002056</v>
+        <v>216.1631311908143</v>
       </c>
       <c r="O25" t="n">
-        <v>14.73295455779512</v>
+        <v>14.70248724504852</v>
       </c>
       <c r="P25" t="n">
-        <v>365.4399827531043</v>
+        <v>365.5061666384207</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -29911,28 +30043,28 @@
         <v>0.0737</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4400819647699705</v>
+        <v>-0.4502886767352934</v>
       </c>
       <c r="J26" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K26" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L26" t="n">
-        <v>0.03753724951722326</v>
+        <v>0.03954744083954431</v>
       </c>
       <c r="M26" t="n">
-        <v>12.88502625964096</v>
+        <v>12.86536505160182</v>
       </c>
       <c r="N26" t="n">
-        <v>254.4778691348329</v>
+        <v>253.7241053719017</v>
       </c>
       <c r="O26" t="n">
-        <v>15.95236249383874</v>
+        <v>15.92871951450906</v>
       </c>
       <c r="P26" t="n">
-        <v>359.3924481649108</v>
+        <v>359.5045550228523</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -29989,28 +30121,28 @@
         <v>0.0769</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.5580782414195975</v>
+        <v>-0.5630464863051753</v>
       </c>
       <c r="J27" t="n">
+        <v>203</v>
+      </c>
+      <c r="K27" t="n">
         <v>202</v>
       </c>
-      <c r="K27" t="n">
-        <v>201</v>
-      </c>
       <c r="L27" t="n">
-        <v>0.05249904071058609</v>
+        <v>0.05389676094747586</v>
       </c>
       <c r="M27" t="n">
-        <v>13.25280993860569</v>
+        <v>13.20761209983602</v>
       </c>
       <c r="N27" t="n">
-        <v>287.3483681965056</v>
+        <v>286.0466525633325</v>
       </c>
       <c r="O27" t="n">
-        <v>16.95135299014523</v>
+        <v>16.91291378099388</v>
       </c>
       <c r="P27" t="n">
-        <v>353.0584283875043</v>
+        <v>353.1129916880972</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -30067,28 +30199,28 @@
         <v>0.09089999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.6343305597989398</v>
+        <v>-0.6338125423468437</v>
       </c>
       <c r="J28" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K28" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L28" t="n">
-        <v>0.05739097668253956</v>
+        <v>0.05786822138134917</v>
       </c>
       <c r="M28" t="n">
-        <v>14.43235673083436</v>
+        <v>14.36311459858174</v>
       </c>
       <c r="N28" t="n">
-        <v>338.172830945188</v>
+        <v>336.49169640874</v>
       </c>
       <c r="O28" t="n">
-        <v>18.38947609218893</v>
+        <v>18.34370999576531</v>
       </c>
       <c r="P28" t="n">
-        <v>347.6410126326404</v>
+        <v>347.6353173518766</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -30145,28 +30277,28 @@
         <v>0.0786</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.5619744307195225</v>
+        <v>-0.5614367741502244</v>
       </c>
       <c r="J29" t="n">
+        <v>203</v>
+      </c>
+      <c r="K29" t="n">
         <v>202</v>
       </c>
-      <c r="K29" t="n">
-        <v>201</v>
-      </c>
       <c r="L29" t="n">
-        <v>0.05533122057838347</v>
+        <v>0.05577254956889954</v>
       </c>
       <c r="M29" t="n">
-        <v>13.49803054079545</v>
+        <v>13.43393273585448</v>
       </c>
       <c r="N29" t="n">
-        <v>281.3013663416576</v>
+        <v>279.9102453705912</v>
       </c>
       <c r="O29" t="n">
-        <v>16.77204120975314</v>
+        <v>16.73051838319994</v>
       </c>
       <c r="P29" t="n">
-        <v>342.4456457313737</v>
+        <v>342.4398084793855</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -30223,28 +30355,28 @@
         <v>0.0825</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.6601865630468664</v>
+        <v>-0.6669177610027669</v>
       </c>
       <c r="J30" t="n">
+        <v>203</v>
+      </c>
+      <c r="K30" t="n">
         <v>202</v>
       </c>
-      <c r="K30" t="n">
-        <v>201</v>
-      </c>
       <c r="L30" t="n">
-        <v>0.0672902864838919</v>
+        <v>0.0691921048971228</v>
       </c>
       <c r="M30" t="n">
-        <v>14.04200801557696</v>
+        <v>14.00765823364709</v>
       </c>
       <c r="N30" t="n">
-        <v>313.5622209644345</v>
+        <v>312.2371652252126</v>
       </c>
       <c r="O30" t="n">
-        <v>17.70768818802823</v>
+        <v>17.67023387579272</v>
       </c>
       <c r="P30" t="n">
-        <v>340.0701538330853</v>
+        <v>340.143464464247</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -30301,28 +30433,28 @@
         <v>0.06809999999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.7544750977047663</v>
+        <v>-0.7596663186629853</v>
       </c>
       <c r="J31" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K31" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L31" t="n">
-        <v>0.07177359272889594</v>
+        <v>0.07336496971327389</v>
       </c>
       <c r="M31" t="n">
-        <v>15.77042881143016</v>
+        <v>15.71853905402385</v>
       </c>
       <c r="N31" t="n">
-        <v>383.055000050593</v>
+        <v>381.2663945695616</v>
       </c>
       <c r="O31" t="n">
-        <v>19.57179092598817</v>
+        <v>19.52604400716032</v>
       </c>
       <c r="P31" t="n">
-        <v>338.0713303458558</v>
+        <v>338.1280632703479</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -30379,28 +30511,28 @@
         <v>0.1625</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.6337914506349602</v>
+        <v>-0.652107829060209</v>
       </c>
       <c r="J32" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K32" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L32" t="n">
-        <v>0.04765938179657825</v>
+        <v>0.05061116052710302</v>
       </c>
       <c r="M32" t="n">
-        <v>16.68770303976243</v>
+        <v>16.69209177897867</v>
       </c>
       <c r="N32" t="n">
-        <v>414.1877072436573</v>
+        <v>413.7675258436651</v>
       </c>
       <c r="O32" t="n">
-        <v>20.35160208051585</v>
+        <v>20.34127640645161</v>
       </c>
       <c r="P32" t="n">
-        <v>333.0223145787439</v>
+        <v>333.2241379681084</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -30457,28 +30589,28 @@
         <v>0.0556</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.7238545453931227</v>
+        <v>-0.7460023265755857</v>
       </c>
       <c r="J33" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K33" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L33" t="n">
-        <v>0.05532875813538052</v>
+        <v>0.0588698759726497</v>
       </c>
       <c r="M33" t="n">
-        <v>16.75122957407799</v>
+        <v>16.76736423567039</v>
       </c>
       <c r="N33" t="n">
-        <v>459.1000454946437</v>
+        <v>459.1055512533104</v>
       </c>
       <c r="O33" t="n">
-        <v>21.42662002030753</v>
+        <v>21.42674849932463</v>
       </c>
       <c r="P33" t="n">
-        <v>330.8881017836516</v>
+        <v>331.1315389700078</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -30535,28 +30667,28 @@
         <v>0.0582</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.193555205330537</v>
+        <v>-1.219184740828925</v>
       </c>
       <c r="J34" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K34" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L34" t="n">
-        <v>0.1010820660768738</v>
+        <v>0.1055582328792229</v>
       </c>
       <c r="M34" t="n">
-        <v>20.27783847634707</v>
+        <v>20.31438782808745</v>
       </c>
       <c r="N34" t="n">
-        <v>649.4865487240631</v>
+        <v>649.3228731014628</v>
       </c>
       <c r="O34" t="n">
-        <v>25.48502597063741</v>
+        <v>25.48181455668852</v>
       </c>
       <c r="P34" t="n">
-        <v>330.7316275492288</v>
+        <v>331.0130181621681</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
@@ -30613,28 +30745,28 @@
         <v>0.0295</v>
       </c>
       <c r="I35" t="n">
-        <v>-2.294914885105153</v>
+        <v>-2.295105672210842</v>
       </c>
       <c r="J35" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K35" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L35" t="n">
-        <v>0.1905428634156229</v>
+        <v>0.1922081194561668</v>
       </c>
       <c r="M35" t="n">
-        <v>26.65859307451672</v>
+        <v>26.52488063882174</v>
       </c>
       <c r="N35" t="n">
-        <v>1140.748334027452</v>
+        <v>1134.987154015253</v>
       </c>
       <c r="O35" t="n">
-        <v>33.77496608477131</v>
+        <v>33.68957040413625</v>
       </c>
       <c r="P35" t="n">
-        <v>336.4060772965506</v>
+        <v>336.4081795393321</v>
       </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
@@ -30691,28 +30823,28 @@
         <v>0.0326</v>
       </c>
       <c r="I36" t="n">
-        <v>-3.617683205334486</v>
+        <v>-3.592302685146141</v>
       </c>
       <c r="J36" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K36" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L36" t="n">
-        <v>0.2336606891547227</v>
+        <v>0.2328914019270467</v>
       </c>
       <c r="M36" t="n">
-        <v>38.12308164700619</v>
+        <v>38.0284174400116</v>
       </c>
       <c r="N36" t="n">
-        <v>2202.717053418196</v>
+        <v>2194.093615723689</v>
       </c>
       <c r="O36" t="n">
-        <v>46.93311254773324</v>
+        <v>46.8411530144561</v>
       </c>
       <c r="P36" t="n">
-        <v>346.8041752127994</v>
+        <v>346.5263746304072</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -30776,7 +30908,7 @@
         <v>-6.491140615603809</v>
       </c>
       <c r="J37" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K37" t="n">
         <v>189</v>
@@ -30855,28 +30987,28 @@
         <v>0.0218</v>
       </c>
       <c r="I38" t="n">
-        <v>-2.05581249474212</v>
+        <v>-2.078270308491466</v>
       </c>
       <c r="J38" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K38" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L38" t="n">
-        <v>0.2224313861221728</v>
+        <v>0.2276944117124049</v>
       </c>
       <c r="M38" t="n">
-        <v>22.20987945312435</v>
+        <v>22.17799497098862</v>
       </c>
       <c r="N38" t="n">
-        <v>755.4701845193448</v>
+        <v>753.6408826527145</v>
       </c>
       <c r="O38" t="n">
-        <v>27.48581787976019</v>
+        <v>27.45252051547753</v>
       </c>
       <c r="P38" t="n">
-        <v>333.0534085524732</v>
+        <v>333.2997809610646</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -30940,7 +31072,7 @@
         <v>-2.972890595792747</v>
       </c>
       <c r="J39" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K39" t="n">
         <v>179</v>
@@ -31000,7 +31132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN203"/>
+  <dimension ref="A1:AN204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71433,6 +71565,200 @@
         </is>
       </c>
     </row>
+    <row r="204">
+      <c r="A204" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:05:44+00:00</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>-36.11619085388189,175.42488922921254</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>-36.11686177754082,175.42454716666595</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>-36.117539528107145,175.42422589652048</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>-36.11821531125281,175.42389865674605</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>-36.1189406765703,175.42356970835195</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>-36.119705149557184,175.42320535389632</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>-36.12046727121186,175.42304408662847</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>-36.12118519412894,175.4229103618894</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>-36.1219046080322,175.42279285795644</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>-36.12262937408783,175.42273339747504</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>-36.123366134594214,175.4228039301633</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>-36.12409975061064,175.4228404782501</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>-36.12487358365762,175.4227791866178</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>-36.125643683913324,175.4229715263768</t>
+        </is>
+      </c>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>-36.12639164049012,175.42305458172402</t>
+        </is>
+      </c>
+      <c r="Q204" t="inlineStr">
+        <is>
+          <t>-36.12710480530617,175.4232240826939</t>
+        </is>
+      </c>
+      <c r="R204" t="inlineStr">
+        <is>
+          <t>-36.12782320320935,175.4233663493709</t>
+        </is>
+      </c>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>-36.128522092396246,175.42360998659987</t>
+        </is>
+      </c>
+      <c r="T204" t="inlineStr">
+        <is>
+          <t>-36.12921816815281,175.42386821449333</t>
+        </is>
+      </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>-36.129918312530585,175.42410526103654</t>
+        </is>
+      </c>
+      <c r="V204" t="inlineStr">
+        <is>
+          <t>-36.1306061206537,175.42440639650445</t>
+        </is>
+      </c>
+      <c r="W204" t="inlineStr">
+        <is>
+          <t>-36.13132906100821,175.4245248862982</t>
+        </is>
+      </c>
+      <c r="X204" t="inlineStr">
+        <is>
+          <t>-36.13199082375593,175.424961335373</t>
+        </is>
+      </c>
+      <c r="Y204" t="inlineStr">
+        <is>
+          <t>-36.13270329550024,175.42520531811428</t>
+        </is>
+      </c>
+      <c r="Z204" t="inlineStr">
+        <is>
+          <t>-36.133412097751865,175.4255123266253</t>
+        </is>
+      </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>-36.13406516237042,175.4259112300112</t>
+        </is>
+      </c>
+      <c r="AB204" t="inlineStr">
+        <is>
+          <t>-36.13470707793316,175.42633120996268</t>
+        </is>
+      </c>
+      <c r="AC204" t="inlineStr">
+        <is>
+          <t>-36.135355000737825,175.42673840998222</t>
+        </is>
+      </c>
+      <c r="AD204" t="inlineStr">
+        <is>
+          <t>-36.136043919654696,175.42705845717472</t>
+        </is>
+      </c>
+      <c r="AE204" t="inlineStr">
+        <is>
+          <t>-36.136690205338944,175.42746911508922</t>
+        </is>
+      </c>
+      <c r="AF204" t="inlineStr">
+        <is>
+          <t>-36.13739723434466,175.427768096983</t>
+        </is>
+      </c>
+      <c r="AG204" t="inlineStr">
+        <is>
+          <t>-36.1380763114831,175.42816630452566</t>
+        </is>
+      </c>
+      <c r="AH204" t="inlineStr">
+        <is>
+          <t>-36.13877579908678,175.4285228602446</t>
+        </is>
+      </c>
+      <c r="AI204" t="inlineStr">
+        <is>
+          <t>-36.13937433926215,175.42903023453934</t>
+        </is>
+      </c>
+      <c r="AJ204" t="inlineStr">
+        <is>
+          <t>-36.13998208724567,175.42952088328366</t>
+        </is>
+      </c>
+      <c r="AK204" t="inlineStr"/>
+      <c r="AL204" t="inlineStr">
+        <is>
+          <t>-36.14128205227441,175.43034879885627</t>
+        </is>
+      </c>
+      <c r="AM204" t="inlineStr"/>
+      <c r="AN204" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0114/nzd0114.xlsx
+++ b/data/nzd0114/nzd0114.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN204"/>
+  <dimension ref="A1:AN205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25789,7 +25789,7 @@
         <v>262.7</v>
       </c>
       <c r="AM203" t="n">
-        <v>306.53</v>
+        <v>263.5</v>
       </c>
       <c r="AN203" t="inlineStr">
         <is>
@@ -25840,7 +25840,7 @@
         <v>310.74</v>
       </c>
       <c r="N204" t="n">
-        <v>316.12</v>
+        <v>325.97</v>
       </c>
       <c r="O204" t="n">
         <v>324.08</v>
@@ -25912,8 +25912,136 @@
       <c r="AL204" t="n">
         <v>258.38</v>
       </c>
-      <c r="AM204" t="inlineStr"/>
+      <c r="AM204" t="n">
+        <v>220.46</v>
+      </c>
       <c r="AN204" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>290.79</v>
+      </c>
+      <c r="C205" t="n">
+        <v>285.67</v>
+      </c>
+      <c r="D205" t="n">
+        <v>287.74</v>
+      </c>
+      <c r="E205" t="n">
+        <v>287.13</v>
+      </c>
+      <c r="F205" t="n">
+        <v>294</v>
+      </c>
+      <c r="G205" t="n">
+        <v>287.82</v>
+      </c>
+      <c r="H205" t="n">
+        <v>287.37</v>
+      </c>
+      <c r="I205" t="n">
+        <v>281.8</v>
+      </c>
+      <c r="J205" t="n">
+        <v>280.78</v>
+      </c>
+      <c r="K205" t="n">
+        <v>288.21</v>
+      </c>
+      <c r="L205" t="n">
+        <v>297.81</v>
+      </c>
+      <c r="M205" t="n">
+        <v>309.64</v>
+      </c>
+      <c r="N205" t="n">
+        <v>336.33</v>
+      </c>
+      <c r="O205" t="n">
+        <v>325.52</v>
+      </c>
+      <c r="P205" t="n">
+        <v>314.15</v>
+      </c>
+      <c r="Q205" t="n">
+        <v>312.29</v>
+      </c>
+      <c r="R205" t="n">
+        <v>307.75</v>
+      </c>
+      <c r="S205" t="n">
+        <v>311.4</v>
+      </c>
+      <c r="T205" t="n">
+        <v>318.03</v>
+      </c>
+      <c r="U205" t="n">
+        <v>329.88</v>
+      </c>
+      <c r="V205" t="n">
+        <v>331.92</v>
+      </c>
+      <c r="W205" t="n">
+        <v>312.93</v>
+      </c>
+      <c r="X205" t="n">
+        <v>365.96</v>
+      </c>
+      <c r="Y205" t="n">
+        <v>355</v>
+      </c>
+      <c r="Z205" t="n">
+        <v>343.17</v>
+      </c>
+      <c r="AA205" t="n">
+        <v>331.84</v>
+      </c>
+      <c r="AB205" t="n">
+        <v>328.39</v>
+      </c>
+      <c r="AC205" t="n">
+        <v>320.78</v>
+      </c>
+      <c r="AD205" t="n">
+        <v>312.03</v>
+      </c>
+      <c r="AE205" t="n">
+        <v>310.53</v>
+      </c>
+      <c r="AF205" t="n">
+        <v>309.39</v>
+      </c>
+      <c r="AG205" t="n">
+        <v>306.37</v>
+      </c>
+      <c r="AH205" t="n">
+        <v>290.02</v>
+      </c>
+      <c r="AI205" t="n">
+        <v>270.44</v>
+      </c>
+      <c r="AJ205" t="n">
+        <v>257.06</v>
+      </c>
+      <c r="AK205" t="n">
+        <v>233.12</v>
+      </c>
+      <c r="AL205" t="n">
+        <v>245.52</v>
+      </c>
+      <c r="AM205" t="n">
+        <v>192.71</v>
+      </c>
+      <c r="AN205" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -25930,7 +26058,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B207"/>
+  <dimension ref="A1:B208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28003,6 +28131,16 @@
       </c>
       <c r="B207" t="n">
         <v>0.49</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>-0.58</v>
       </c>
     </row>
   </sheetData>
@@ -28171,28 +28309,28 @@
         <v>0.0582</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2517771342004353</v>
+        <v>0.2566284607442066</v>
       </c>
       <c r="J2" t="n">
+        <v>204</v>
+      </c>
+      <c r="K2" t="n">
         <v>203</v>
       </c>
-      <c r="K2" t="n">
-        <v>202</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.02487710330816029</v>
+        <v>0.02606626527596334</v>
       </c>
       <c r="M2" t="n">
-        <v>9.610358766989165</v>
+        <v>9.588752334360088</v>
       </c>
       <c r="N2" t="n">
-        <v>130.4398199390647</v>
+        <v>129.9134324315208</v>
       </c>
       <c r="O2" t="n">
-        <v>11.42102534534727</v>
+        <v>11.3979573797905</v>
       </c>
       <c r="P2" t="n">
-        <v>279.2065387294568</v>
+        <v>279.1532956176703</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -28249,28 +28387,28 @@
         <v>0.0562</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3832935562952899</v>
+        <v>0.3855322269360137</v>
       </c>
       <c r="J3" t="n">
+        <v>204</v>
+      </c>
+      <c r="K3" t="n">
         <v>203</v>
       </c>
-      <c r="K3" t="n">
-        <v>202</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.0452553308895276</v>
+        <v>0.04622133707248166</v>
       </c>
       <c r="M3" t="n">
-        <v>10.67936833967052</v>
+        <v>10.63691895929349</v>
       </c>
       <c r="N3" t="n">
-        <v>162.7041416694421</v>
+        <v>161.9273814739376</v>
       </c>
       <c r="O3" t="n">
-        <v>12.75555336586548</v>
+        <v>12.7250690164705</v>
       </c>
       <c r="P3" t="n">
-        <v>273.2331527824949</v>
+        <v>273.2085834631341</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -28327,28 +28465,28 @@
         <v>0.0536</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3357678885646431</v>
+        <v>0.3391040250568816</v>
       </c>
       <c r="J4" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K4" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03396595007975267</v>
+        <v>0.03496620397708639</v>
       </c>
       <c r="M4" t="n">
-        <v>10.81286229269379</v>
+        <v>10.77513162249473</v>
       </c>
       <c r="N4" t="n">
-        <v>168.8196243839638</v>
+        <v>168.0391082283922</v>
       </c>
       <c r="O4" t="n">
-        <v>12.99306062419335</v>
+        <v>12.96298994169139</v>
       </c>
       <c r="P4" t="n">
-        <v>275.448204252591</v>
+        <v>275.4115974906641</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -28405,28 +28543,28 @@
         <v>0.0601</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2514396124712802</v>
+        <v>0.2493250642253868</v>
       </c>
       <c r="J5" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K5" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01890880616787138</v>
+        <v>0.01879207879805067</v>
       </c>
       <c r="M5" t="n">
-        <v>10.89938454734707</v>
+        <v>10.85638032277797</v>
       </c>
       <c r="N5" t="n">
-        <v>169.6315614326128</v>
+        <v>168.8134042579661</v>
       </c>
       <c r="O5" t="n">
-        <v>13.02426817263115</v>
+        <v>12.99282125860146</v>
       </c>
       <c r="P5" t="n">
-        <v>282.5601317128724</v>
+        <v>282.5835763925651</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -28483,28 +28621,28 @@
         <v>0.0604</v>
       </c>
       <c r="I6" t="n">
-        <v>0.06431105297154326</v>
+        <v>0.0663421046500139</v>
       </c>
       <c r="J6" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K6" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001185974948622603</v>
+        <v>0.001275340185808105</v>
       </c>
       <c r="M6" t="n">
-        <v>11.38210962444475</v>
+        <v>11.33442036943741</v>
       </c>
       <c r="N6" t="n">
-        <v>180.4891985583007</v>
+        <v>179.6068062074049</v>
       </c>
       <c r="O6" t="n">
-        <v>13.43462684849493</v>
+        <v>13.40174638647534</v>
       </c>
       <c r="P6" t="n">
-        <v>290.2779393144054</v>
+        <v>290.2553703858799</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -28561,28 +28699,28 @@
         <v>0.0414</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3119063664218869</v>
+        <v>0.3087661231735764</v>
       </c>
       <c r="J7" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K7" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01949338992259042</v>
+        <v>0.01931008165209525</v>
       </c>
       <c r="M7" t="n">
-        <v>13.43392992904797</v>
+        <v>13.38314991959459</v>
       </c>
       <c r="N7" t="n">
-        <v>248.2375322658199</v>
+        <v>247.0427215832053</v>
       </c>
       <c r="O7" t="n">
-        <v>15.75555560003581</v>
+        <v>15.7175927413585</v>
       </c>
       <c r="P7" t="n">
-        <v>282.6029525674737</v>
+        <v>282.6382531796153</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -28639,28 +28777,28 @@
         <v>0.0535</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2054887796477338</v>
+        <v>0.2061781020712798</v>
       </c>
       <c r="J8" t="n">
+        <v>204</v>
+      </c>
+      <c r="K8" t="n">
         <v>203</v>
       </c>
-      <c r="K8" t="n">
-        <v>202</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.00859906019300416</v>
+        <v>0.008748844712888726</v>
       </c>
       <c r="M8" t="n">
-        <v>13.05891762594158</v>
+        <v>12.99768680475888</v>
       </c>
       <c r="N8" t="n">
-        <v>251.2927608377186</v>
+        <v>250.0571520584674</v>
       </c>
       <c r="O8" t="n">
-        <v>15.85221627526317</v>
+        <v>15.81319550433964</v>
       </c>
       <c r="P8" t="n">
-        <v>281.2188873540921</v>
+        <v>281.21124913192</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -28717,28 +28855,28 @@
         <v>0.0598</v>
       </c>
       <c r="I9" t="n">
-        <v>0.06264580150177057</v>
+        <v>0.05978419711761183</v>
       </c>
       <c r="J9" t="n">
+        <v>204</v>
+      </c>
+      <c r="K9" t="n">
         <v>203</v>
       </c>
-      <c r="K9" t="n">
-        <v>202</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.001163711424088887</v>
+        <v>0.001071114697368092</v>
       </c>
       <c r="M9" t="n">
-        <v>11.04052881558215</v>
+        <v>10.99872269317829</v>
       </c>
       <c r="N9" t="n">
-        <v>173.875490890328</v>
+        <v>173.0583674822135</v>
       </c>
       <c r="O9" t="n">
-        <v>13.18618560806452</v>
+        <v>13.15516504959985</v>
       </c>
       <c r="P9" t="n">
-        <v>282.9861939060148</v>
+        <v>283.0179026816302</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -28795,28 +28933,28 @@
         <v>0.0436</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.167169500808194</v>
+        <v>-0.1706424925438497</v>
       </c>
       <c r="J10" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K10" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L10" t="n">
-        <v>0.007822407034739243</v>
+        <v>0.00823359719283101</v>
       </c>
       <c r="M10" t="n">
-        <v>11.02818794682824</v>
+        <v>10.98985282785205</v>
       </c>
       <c r="N10" t="n">
-        <v>179.3750474965777</v>
+        <v>178.5434068883175</v>
       </c>
       <c r="O10" t="n">
-        <v>13.3930970091528</v>
+        <v>13.3620135791099</v>
       </c>
       <c r="P10" t="n">
-        <v>288.6221003648029</v>
+        <v>288.6610657847006</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -28873,28 +29011,28 @@
         <v>0.057</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.02091541175344186</v>
+        <v>-0.02064067212198165</v>
       </c>
       <c r="J11" t="n">
+        <v>204</v>
+      </c>
+      <c r="K11" t="n">
         <v>203</v>
       </c>
-      <c r="K11" t="n">
-        <v>202</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.0001242948119333231</v>
+        <v>0.000122356843401783</v>
       </c>
       <c r="M11" t="n">
-        <v>11.37417771494022</v>
+        <v>11.31951594760496</v>
       </c>
       <c r="N11" t="n">
-        <v>181.6482702511477</v>
+        <v>180.7538144202391</v>
       </c>
       <c r="O11" t="n">
-        <v>13.47769528707144</v>
+        <v>13.44447151881542</v>
       </c>
       <c r="P11" t="n">
-        <v>288.4920022121308</v>
+        <v>288.4889578858869</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -28951,28 +29089,28 @@
         <v>0.0868</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0004285480097116548</v>
+        <v>0.002186084356372342</v>
       </c>
       <c r="J12" t="n">
+        <v>204</v>
+      </c>
+      <c r="K12" t="n">
         <v>203</v>
       </c>
-      <c r="K12" t="n">
-        <v>202</v>
-      </c>
       <c r="L12" t="n">
-        <v>4.260352315377247e-08</v>
+        <v>1.120498349660437e-06</v>
       </c>
       <c r="M12" t="n">
-        <v>12.58583311098151</v>
+        <v>12.53197545162541</v>
       </c>
       <c r="N12" t="n">
-        <v>222.5147712474127</v>
+        <v>221.4335039595509</v>
       </c>
       <c r="O12" t="n">
-        <v>14.91692901529711</v>
+        <v>14.88064192027854</v>
       </c>
       <c r="P12" t="n">
-        <v>296.0528525239646</v>
+        <v>296.0333776706408</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -29029,28 +29167,28 @@
         <v>0.0509</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.0358495564344643</v>
+        <v>-0.03531087792140868</v>
       </c>
       <c r="J13" t="n">
+        <v>204</v>
+      </c>
+      <c r="K13" t="n">
         <v>203</v>
       </c>
-      <c r="K13" t="n">
-        <v>202</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.00024928643546962</v>
+        <v>0.000244460318022055</v>
       </c>
       <c r="M13" t="n">
-        <v>13.20542216938256</v>
+        <v>13.14314231480186</v>
       </c>
       <c r="N13" t="n">
-        <v>266.0517149349351</v>
+        <v>264.7425117339615</v>
       </c>
       <c r="O13" t="n">
-        <v>16.31109177630164</v>
+        <v>16.27090998481528</v>
       </c>
       <c r="P13" t="n">
-        <v>310.0608526158234</v>
+        <v>310.0548836439439</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -29107,28 +29245,28 @@
         <v>0.0503</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.02537552612876463</v>
+        <v>-0.003893364910154917</v>
       </c>
       <c r="J14" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K14" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0001424736916942893</v>
+        <v>3.38594094595468e-06</v>
       </c>
       <c r="M14" t="n">
-        <v>12.31192822292957</v>
+        <v>12.29011524926477</v>
       </c>
       <c r="N14" t="n">
-        <v>234.1210235190603</v>
+        <v>233.2651443910778</v>
       </c>
       <c r="O14" t="n">
-        <v>15.30101380690379</v>
+        <v>15.27302014635867</v>
       </c>
       <c r="P14" t="n">
-        <v>325.2298532941687</v>
+        <v>324.9927662714318</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -29185,28 +29323,28 @@
         <v>0.0624</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.08876017503908699</v>
+        <v>-0.08552527751644212</v>
       </c>
       <c r="J15" t="n">
+        <v>204</v>
+      </c>
+      <c r="K15" t="n">
         <v>203</v>
       </c>
-      <c r="K15" t="n">
-        <v>202</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.002014287587355557</v>
+        <v>0.001890077462698203</v>
       </c>
       <c r="M15" t="n">
-        <v>11.51976988275669</v>
+        <v>11.48263323519372</v>
       </c>
       <c r="N15" t="n">
-        <v>201.4858546650232</v>
+        <v>200.5436711486103</v>
       </c>
       <c r="O15" t="n">
-        <v>14.19457130966001</v>
+        <v>14.1613442564119</v>
       </c>
       <c r="P15" t="n">
-        <v>324.6557612398333</v>
+        <v>324.6199160893813</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -29263,28 +29401,28 @@
         <v>0.0615</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.08744786018344995</v>
+        <v>-0.08711226668543381</v>
       </c>
       <c r="J16" t="n">
+        <v>204</v>
+      </c>
+      <c r="K16" t="n">
         <v>203</v>
       </c>
-      <c r="K16" t="n">
-        <v>202</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.002104423888428242</v>
+        <v>0.002110813652520083</v>
       </c>
       <c r="M16" t="n">
-        <v>11.1792139536059</v>
+        <v>11.12593157700034</v>
       </c>
       <c r="N16" t="n">
-        <v>187.1783707019169</v>
+        <v>186.2568517276803</v>
       </c>
       <c r="O16" t="n">
-        <v>13.68131465546776</v>
+        <v>13.64759508952696</v>
       </c>
       <c r="P16" t="n">
-        <v>316.1440239239797</v>
+        <v>316.1403052901303</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -29341,28 +29479,28 @@
         <v>0.0573</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2511898395142058</v>
+        <v>-0.2477073955242607</v>
       </c>
       <c r="J17" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K17" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L17" t="n">
-        <v>0.01439685811534863</v>
+        <v>0.01415097448324121</v>
       </c>
       <c r="M17" t="n">
-        <v>12.36629532204194</v>
+        <v>12.32464717981695</v>
       </c>
       <c r="N17" t="n">
-        <v>223.1843891836421</v>
+        <v>222.1380496463577</v>
       </c>
       <c r="O17" t="n">
-        <v>14.93935705389098</v>
+        <v>14.9042963485821</v>
       </c>
       <c r="P17" t="n">
-        <v>315.5030116606511</v>
+        <v>315.4643795017189</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -29419,28 +29557,28 @@
         <v>0.0537</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1489299329453465</v>
+        <v>-0.1489322869998546</v>
       </c>
       <c r="J18" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K18" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L18" t="n">
-        <v>0.005216209382864712</v>
+        <v>0.005272122290299386</v>
       </c>
       <c r="M18" t="n">
-        <v>12.2021762697172</v>
+        <v>12.14147799863262</v>
       </c>
       <c r="N18" t="n">
-        <v>218.7964108339274</v>
+        <v>217.7078715033763</v>
       </c>
       <c r="O18" t="n">
-        <v>14.79176834708844</v>
+        <v>14.75492702467133</v>
       </c>
       <c r="P18" t="n">
-        <v>311.7141265432215</v>
+        <v>311.7141526852124</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -29497,28 +29635,28 @@
         <v>0.0545</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.03811589016516204</v>
+        <v>-0.03667094226820612</v>
       </c>
       <c r="J19" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K19" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0003011316028920241</v>
+        <v>0.0002817639062063781</v>
       </c>
       <c r="M19" t="n">
-        <v>12.81760570607729</v>
+        <v>12.76252143445991</v>
       </c>
       <c r="N19" t="n">
-        <v>244.0753562128295</v>
+        <v>242.8768173603351</v>
       </c>
       <c r="O19" t="n">
-        <v>15.62291125919972</v>
+        <v>15.5845056822581</v>
       </c>
       <c r="P19" t="n">
-        <v>311.0027863665168</v>
+        <v>310.9865746949033</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -29575,28 +29713,28 @@
         <v>0.0533</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.03078616374370053</v>
+        <v>-0.02615142817400212</v>
       </c>
       <c r="J20" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K20" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0001901724858339726</v>
+        <v>0.0001386751364667038</v>
       </c>
       <c r="M20" t="n">
-        <v>12.82510862095011</v>
+        <v>12.78684672764352</v>
       </c>
       <c r="N20" t="n">
-        <v>256.3244532658518</v>
+        <v>255.1571975032771</v>
       </c>
       <c r="O20" t="n">
-        <v>16.01013595400901</v>
+        <v>15.97364070909563</v>
       </c>
       <c r="P20" t="n">
-        <v>314.2849303571303</v>
+        <v>314.233561196846</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -29653,28 +29791,28 @@
         <v>0.0487</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1489622310377812</v>
+        <v>-0.1375133323413787</v>
       </c>
       <c r="J21" t="n">
+        <v>204</v>
+      </c>
+      <c r="K21" t="n">
         <v>203</v>
       </c>
-      <c r="K21" t="n">
-        <v>202</v>
-      </c>
       <c r="L21" t="n">
-        <v>0.004796087123760784</v>
+        <v>0.004123236173786737</v>
       </c>
       <c r="M21" t="n">
-        <v>12.43469510626394</v>
+        <v>12.43953577576492</v>
       </c>
       <c r="N21" t="n">
-        <v>236.6736174944722</v>
+        <v>236.1340672425361</v>
       </c>
       <c r="O21" t="n">
-        <v>15.38420025527724</v>
+        <v>15.3666543932808</v>
       </c>
       <c r="P21" t="n">
-        <v>322.4679240204202</v>
+        <v>322.3407827701752</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -29731,28 +29869,28 @@
         <v>0.0493</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2504636431590707</v>
+        <v>-0.2433086153314654</v>
       </c>
       <c r="J22" t="n">
+        <v>204</v>
+      </c>
+      <c r="K22" t="n">
         <v>203</v>
       </c>
-      <c r="K22" t="n">
-        <v>202</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.01269446318152789</v>
+        <v>0.01210452219960056</v>
       </c>
       <c r="M22" t="n">
-        <v>12.64251294272251</v>
+        <v>12.61964508214004</v>
       </c>
       <c r="N22" t="n">
-        <v>250.7835930452864</v>
+        <v>249.7928293964396</v>
       </c>
       <c r="O22" t="n">
-        <v>15.83614830207416</v>
+        <v>15.80483563332563</v>
       </c>
       <c r="P22" t="n">
-        <v>331.4719240419641</v>
+        <v>331.3924666891076</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -29809,28 +29947,28 @@
         <v>0.0539</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.4668504847306611</v>
+        <v>-0.4850674070010437</v>
       </c>
       <c r="J23" t="n">
+        <v>204</v>
+      </c>
+      <c r="K23" t="n">
         <v>203</v>
       </c>
-      <c r="K23" t="n">
-        <v>202</v>
-      </c>
       <c r="L23" t="n">
-        <v>0.04392885003112301</v>
+        <v>0.04745044902028417</v>
       </c>
       <c r="M23" t="n">
-        <v>12.71964640014589</v>
+        <v>12.7363049989509</v>
       </c>
       <c r="N23" t="n">
-        <v>243.8195404124703</v>
+        <v>244.2041754419427</v>
       </c>
       <c r="O23" t="n">
-        <v>15.61472191274857</v>
+        <v>15.62703348182062</v>
       </c>
       <c r="P23" t="n">
-        <v>343.416313584235</v>
+        <v>343.6186144635152</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -29887,28 +30025,28 @@
         <v>0.0592</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.4049870899239543</v>
+        <v>-0.381686261197309</v>
       </c>
       <c r="J24" t="n">
+        <v>204</v>
+      </c>
+      <c r="K24" t="n">
         <v>203</v>
       </c>
-      <c r="K24" t="n">
-        <v>202</v>
-      </c>
       <c r="L24" t="n">
-        <v>0.03322391940073421</v>
+        <v>0.02962629657098825</v>
       </c>
       <c r="M24" t="n">
-        <v>12.70027060501256</v>
+        <v>12.75603588414925</v>
       </c>
       <c r="N24" t="n">
-        <v>245.318269138921</v>
+        <v>246.7040932706505</v>
       </c>
       <c r="O24" t="n">
-        <v>15.66263927755859</v>
+        <v>15.70681677714012</v>
       </c>
       <c r="P24" t="n">
-        <v>353.590231052605</v>
+        <v>353.3314728458458</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -29965,28 +30103,28 @@
         <v>0.0698</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3228865846402686</v>
+        <v>-0.3248285452790581</v>
       </c>
       <c r="J25" t="n">
+        <v>204</v>
+      </c>
+      <c r="K25" t="n">
         <v>203</v>
       </c>
-      <c r="K25" t="n">
-        <v>202</v>
-      </c>
       <c r="L25" t="n">
-        <v>0.02419110213579667</v>
+        <v>0.02473207896816398</v>
       </c>
       <c r="M25" t="n">
-        <v>11.94353142266918</v>
+        <v>11.8933147031108</v>
       </c>
       <c r="N25" t="n">
-        <v>216.1631311908143</v>
+        <v>215.116308246274</v>
       </c>
       <c r="O25" t="n">
-        <v>14.70248724504852</v>
+        <v>14.6668438406589</v>
       </c>
       <c r="P25" t="n">
-        <v>365.5061666384207</v>
+        <v>365.5277323199844</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -30043,28 +30181,28 @@
         <v>0.0737</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4502886767352934</v>
+        <v>-0.4546979610148866</v>
       </c>
       <c r="J26" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K26" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L26" t="n">
-        <v>0.03954744083954431</v>
+        <v>0.04069722674447374</v>
       </c>
       <c r="M26" t="n">
-        <v>12.86536505160182</v>
+        <v>12.82032092770466</v>
       </c>
       <c r="N26" t="n">
-        <v>253.7241053719017</v>
+        <v>252.5613777721994</v>
       </c>
       <c r="O26" t="n">
-        <v>15.92871951450906</v>
+        <v>15.89217976780402</v>
       </c>
       <c r="P26" t="n">
-        <v>359.5045550228523</v>
+        <v>359.553529981795</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -30121,28 +30259,28 @@
         <v>0.0769</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.5630464863051753</v>
+        <v>-0.5694122046652133</v>
       </c>
       <c r="J27" t="n">
+        <v>204</v>
+      </c>
+      <c r="K27" t="n">
         <v>203</v>
       </c>
-      <c r="K27" t="n">
-        <v>202</v>
-      </c>
       <c r="L27" t="n">
-        <v>0.05389676094747586</v>
+        <v>0.05558172677073958</v>
       </c>
       <c r="M27" t="n">
-        <v>13.20761209983602</v>
+        <v>13.16827780688675</v>
       </c>
       <c r="N27" t="n">
-        <v>286.0466525633325</v>
+        <v>284.8311847415212</v>
       </c>
       <c r="O27" t="n">
-        <v>16.91291378099388</v>
+        <v>16.87694239906984</v>
       </c>
       <c r="P27" t="n">
-        <v>353.1129916880972</v>
+        <v>353.1836836745025</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -30199,28 +30337,28 @@
         <v>0.09089999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.6338125423468437</v>
+        <v>-0.6362338658697668</v>
       </c>
       <c r="J28" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K28" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L28" t="n">
-        <v>0.05786822138134917</v>
+        <v>0.05887304358475909</v>
       </c>
       <c r="M28" t="n">
-        <v>14.36311459858174</v>
+        <v>14.30379966139752</v>
       </c>
       <c r="N28" t="n">
-        <v>336.49169640874</v>
+        <v>334.8539927173409</v>
       </c>
       <c r="O28" t="n">
-        <v>18.34370999576531</v>
+        <v>18.29901616801682</v>
       </c>
       <c r="P28" t="n">
-        <v>347.6353173518766</v>
+        <v>347.6622374981317</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -30277,28 +30415,28 @@
         <v>0.0786</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.5614367741502244</v>
+        <v>-0.5681194582773459</v>
       </c>
       <c r="J29" t="n">
+        <v>204</v>
+      </c>
+      <c r="K29" t="n">
         <v>203</v>
       </c>
-      <c r="K29" t="n">
-        <v>202</v>
-      </c>
       <c r="L29" t="n">
-        <v>0.05577254956889954</v>
+        <v>0.05756403317782022</v>
       </c>
       <c r="M29" t="n">
-        <v>13.43393273585448</v>
+        <v>13.40031699304821</v>
       </c>
       <c r="N29" t="n">
-        <v>279.9102453705912</v>
+        <v>278.7516010260463</v>
       </c>
       <c r="O29" t="n">
-        <v>16.73051838319994</v>
+        <v>16.69585580394267</v>
       </c>
       <c r="P29" t="n">
-        <v>342.4398084793855</v>
+        <v>342.5131905790034</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -30355,28 +30493,28 @@
         <v>0.0825</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.6669177610027669</v>
+        <v>-0.6772580204645158</v>
       </c>
       <c r="J30" t="n">
+        <v>204</v>
+      </c>
+      <c r="K30" t="n">
         <v>203</v>
       </c>
-      <c r="K30" t="n">
-        <v>202</v>
-      </c>
       <c r="L30" t="n">
-        <v>0.0691921048971228</v>
+        <v>0.07179640157211875</v>
       </c>
       <c r="M30" t="n">
-        <v>14.00765823364709</v>
+        <v>13.9911215331918</v>
       </c>
       <c r="N30" t="n">
-        <v>312.2371652252126</v>
+        <v>311.2225755387255</v>
       </c>
       <c r="O30" t="n">
-        <v>17.67023387579272</v>
+        <v>17.64150151032291</v>
       </c>
       <c r="P30" t="n">
-        <v>340.143464464247</v>
+        <v>340.2573626066991</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -30433,28 +30571,28 @@
         <v>0.06809999999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.7596663186629853</v>
+        <v>-0.7670719655147789</v>
       </c>
       <c r="J31" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K31" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L31" t="n">
-        <v>0.07336496971327389</v>
+        <v>0.07538132043228019</v>
       </c>
       <c r="M31" t="n">
-        <v>15.71853905402385</v>
+        <v>15.67788127473864</v>
       </c>
       <c r="N31" t="n">
-        <v>381.2663945695616</v>
+        <v>379.6307268671438</v>
       </c>
       <c r="O31" t="n">
-        <v>19.52604400716032</v>
+        <v>19.48411473142015</v>
       </c>
       <c r="P31" t="n">
-        <v>338.1280632703479</v>
+        <v>338.209933262935</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -30511,28 +30649,28 @@
         <v>0.1625</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.652107829060209</v>
+        <v>-0.65867022208362</v>
       </c>
       <c r="J32" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K32" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L32" t="n">
-        <v>0.05061116052710302</v>
+        <v>0.05207825723276849</v>
       </c>
       <c r="M32" t="n">
-        <v>16.69209177897867</v>
+        <v>16.63900804272199</v>
       </c>
       <c r="N32" t="n">
-        <v>413.7675258436651</v>
+        <v>411.8884305719866</v>
       </c>
       <c r="O32" t="n">
-        <v>20.34127640645161</v>
+        <v>20.29503462849932</v>
       </c>
       <c r="P32" t="n">
-        <v>333.2241379681084</v>
+        <v>333.2972852026589</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -30589,28 +30727,28 @@
         <v>0.0556</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.7460023265755857</v>
+        <v>-0.7511103497121921</v>
       </c>
       <c r="J33" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K33" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L33" t="n">
-        <v>0.0588698759726497</v>
+        <v>0.06023442408557134</v>
       </c>
       <c r="M33" t="n">
-        <v>16.76736423567039</v>
+        <v>16.70593804043617</v>
       </c>
       <c r="N33" t="n">
-        <v>459.1055512533104</v>
+        <v>456.8857784025836</v>
       </c>
       <c r="O33" t="n">
-        <v>21.42674849932463</v>
+        <v>21.37488662899955</v>
       </c>
       <c r="P33" t="n">
-        <v>331.1315389700078</v>
+        <v>331.1883196604969</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -30667,28 +30805,28 @@
         <v>0.0582</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.219184740828925</v>
+        <v>-1.22806674179213</v>
       </c>
       <c r="J34" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K34" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L34" t="n">
-        <v>0.1055582328792229</v>
+        <v>0.1079376765511063</v>
       </c>
       <c r="M34" t="n">
-        <v>20.31438782808745</v>
+        <v>20.25874494413302</v>
       </c>
       <c r="N34" t="n">
-        <v>649.3228731014628</v>
+        <v>646.39639062933</v>
       </c>
       <c r="O34" t="n">
-        <v>25.48181455668852</v>
+        <v>25.4243267487918</v>
       </c>
       <c r="P34" t="n">
-        <v>331.0130181621681</v>
+        <v>331.1116326874737</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
@@ -30745,28 +30883,28 @@
         <v>0.0295</v>
       </c>
       <c r="I35" t="n">
-        <v>-2.295105672210842</v>
+        <v>-2.300225703813685</v>
       </c>
       <c r="J35" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K35" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L35" t="n">
-        <v>0.1922081194561668</v>
+        <v>0.1945884580219547</v>
       </c>
       <c r="M35" t="n">
-        <v>26.52488063882174</v>
+        <v>26.41569842612146</v>
       </c>
       <c r="N35" t="n">
-        <v>1134.987154015253</v>
+        <v>1129.406924922723</v>
       </c>
       <c r="O35" t="n">
-        <v>33.68957040413625</v>
+        <v>33.60665001041792</v>
       </c>
       <c r="P35" t="n">
-        <v>336.4081795393321</v>
+        <v>336.4652281575629</v>
       </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
@@ -30823,28 +30961,28 @@
         <v>0.0326</v>
       </c>
       <c r="I36" t="n">
-        <v>-3.592302685146141</v>
+        <v>-3.585918941232686</v>
       </c>
       <c r="J36" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K36" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L36" t="n">
-        <v>0.2328914019270467</v>
+        <v>0.2342896517517425</v>
       </c>
       <c r="M36" t="n">
-        <v>38.0284174400116</v>
+        <v>37.85509639120802</v>
       </c>
       <c r="N36" t="n">
-        <v>2194.093615723689</v>
+        <v>2182.789989835114</v>
       </c>
       <c r="O36" t="n">
-        <v>46.8411530144561</v>
+        <v>46.72033807492316</v>
       </c>
       <c r="P36" t="n">
-        <v>346.5263746304072</v>
+        <v>346.4557198414693</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -30905,28 +31043,28 @@
         <v>0.0211</v>
       </c>
       <c r="I37" t="n">
-        <v>-6.491140615603809</v>
+        <v>-6.465579479790306</v>
       </c>
       <c r="J37" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K37" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L37" t="n">
-        <v>0.3594069974138727</v>
+        <v>0.3600183510498666</v>
       </c>
       <c r="M37" t="n">
-        <v>50.57426456335781</v>
+        <v>50.40484643148691</v>
       </c>
       <c r="N37" t="n">
-        <v>3794.926579683961</v>
+        <v>3777.871424728076</v>
       </c>
       <c r="O37" t="n">
-        <v>61.60297541258832</v>
+        <v>61.46439151840744</v>
       </c>
       <c r="P37" t="n">
-        <v>381.834401595113</v>
+        <v>381.5460622228879</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -30987,28 +31125,28 @@
         <v>0.0218</v>
       </c>
       <c r="I38" t="n">
-        <v>-2.078270308491466</v>
+        <v>-2.114060391723123</v>
       </c>
       <c r="J38" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K38" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L38" t="n">
-        <v>0.2276944117124049</v>
+        <v>0.2345290621381968</v>
       </c>
       <c r="M38" t="n">
-        <v>22.17799497098862</v>
+        <v>22.19994949278469</v>
       </c>
       <c r="N38" t="n">
-        <v>753.6408826527145</v>
+        <v>755.1932614792382</v>
       </c>
       <c r="O38" t="n">
-        <v>27.45252051547753</v>
+        <v>27.48077985573259</v>
       </c>
       <c r="P38" t="n">
-        <v>333.2997809610646</v>
+        <v>333.6967966015841</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -31069,28 +31207,28 @@
         <v>0.0271</v>
       </c>
       <c r="I39" t="n">
-        <v>-2.972890595792747</v>
+        <v>-3.183839795644183</v>
       </c>
       <c r="J39" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K39" t="n">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="L39" t="n">
-        <v>0.269235261265775</v>
+        <v>0.2915668679860686</v>
       </c>
       <c r="M39" t="n">
-        <v>25.33048847840733</v>
+        <v>25.69408727583397</v>
       </c>
       <c r="N39" t="n">
-        <v>1170.812052022341</v>
+        <v>1215.997415206414</v>
       </c>
       <c r="O39" t="n">
-        <v>34.21713097298399</v>
+        <v>34.87115448628585</v>
       </c>
       <c r="P39" t="n">
-        <v>359.3560168812973</v>
+        <v>361.7797935506713</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -31132,7 +31270,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN204"/>
+  <dimension ref="A1:AN205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71556,7 +71694,7 @@
       </c>
       <c r="AM203" t="inlineStr">
         <is>
-          <t>-36.14164473842933,175.43128433813723</t>
+          <t>-36.141862553523396,175.43088888947946</t>
         </is>
       </c>
       <c r="AN203" t="inlineStr">
@@ -71633,7 +71771,7 @@
       </c>
       <c r="N204" t="inlineStr">
         <is>
-          <t>-36.12487358365762,175.4227791866178</t>
+          <t>-36.124873023390556,175.42288858262322</t>
         </is>
       </c>
       <c r="O204" t="inlineStr">
@@ -71752,8 +71890,214 @@
           <t>-36.14128205227441,175.43034879885627</t>
         </is>
       </c>
-      <c r="AM204" t="inlineStr"/>
+      <c r="AM204" t="inlineStr">
+        <is>
+          <t>-36.142080418005506,175.4304933466905</t>
+        </is>
+      </c>
       <c r="AN204" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>-36.116228466366415,175.4250036878046</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>-36.11687909561834,175.4245998674277</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>-36.11755403882672,175.42427005434882</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>-36.11821991141028,175.42391265560855</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>-36.118951988796134,175.42361282064596</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>-36.11971779944442,175.42329282062283</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>-36.12047829415873,175.42316348078145</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>-36.12119216247685,175.42298583909925</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>-36.12191065951939,175.4228584045528</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>-36.12263775853537,175.42282421456073</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>-36.12336706166286,175.4228139720012</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>-36.124098629988346,175.42282833965052</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>-36.12487243400689,175.42300364277935</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>-36.12564135465265,175.4229872599515</t>
+        </is>
+      </c>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>-36.126390268273745,175.4230617142837</t>
+        </is>
+      </c>
+      <c r="Q205" t="inlineStr">
+        <is>
+          <t>-36.12710270538727,175.42323499776592</t>
+        </is>
+      </c>
+      <c r="R205" t="inlineStr">
+        <is>
+          <t>-36.127820708244904,175.42337931788722</t>
+        </is>
+      </c>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t>-36.128521676565285,175.42361214803714</t>
+        </is>
+      </c>
+      <c r="T205" t="inlineStr">
+        <is>
+          <t>-36.129216442437794,175.42387718453122</t>
+        </is>
+      </c>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>-36.12990034827573,175.42419863664125</t>
+        </is>
+      </c>
+      <c r="V205" t="inlineStr">
+        <is>
+          <t>-36.13060464441052,175.42441406979395</t>
+        </is>
+      </c>
+      <c r="W205" t="inlineStr">
+        <is>
+          <t>-36.13135266012366,175.42440222060415</t>
+        </is>
+      </c>
+      <c r="X205" t="inlineStr">
+        <is>
+          <t>-36.13195092261952,175.4251687335748</t>
+        </is>
+      </c>
+      <c r="Y205" t="inlineStr">
+        <is>
+          <t>-36.132690353702884,175.42524595081483</t>
+        </is>
+      </c>
+      <c r="Z205" t="inlineStr">
+        <is>
+          <t>-36.13338708885052,175.42556609563667</t>
+        </is>
+      </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>-36.13407221427655,175.42589624046465</t>
+        </is>
+      </c>
+      <c r="AB205" t="inlineStr">
+        <is>
+          <t>-36.134721000994745,175.42630161503146</t>
+        </is>
+      </c>
+      <c r="AC205" t="inlineStr">
+        <is>
+          <t>-36.13538858801139,175.42666701654437</t>
+        </is>
+      </c>
+      <c r="AD205" t="inlineStr">
+        <is>
+          <t>-36.13606132362038,175.42702146300064</t>
+        </is>
+      </c>
+      <c r="AE205" t="inlineStr">
+        <is>
+          <t>-36.13670128064436,175.4274455731959</t>
+        </is>
+      </c>
+      <c r="AF205" t="inlineStr">
+        <is>
+          <t>-36.13734464648939,175.42787674661662</t>
+        </is>
+      </c>
+      <c r="AG205" t="inlineStr">
+        <is>
+          <t>-36.137997408386155,175.4283169091211</t>
+        </is>
+      </c>
+      <c r="AH205" t="inlineStr">
+        <is>
+          <t>-36.13869617684363,175.42866741644843</t>
+        </is>
+      </c>
+      <c r="AI205" t="inlineStr">
+        <is>
+          <t>-36.13940172374807,175.42898051718936</t>
+        </is>
+      </c>
+      <c r="AJ205" t="inlineStr">
+        <is>
+          <t>-36.14007588328779,175.42935059345976</t>
+        </is>
+      </c>
+      <c r="AK205" t="inlineStr">
+        <is>
+          <t>-36.140803491876724,175.4296236215357</t>
+        </is>
+      </c>
+      <c r="AL205" t="inlineStr">
+        <is>
+          <t>-36.141347148162026,175.43023061465408</t>
+        </is>
+      </c>
+      <c r="AM205" t="inlineStr">
+        <is>
+          <t>-36.14222088527489,175.43023831966212</t>
+        </is>
+      </c>
+      <c r="AN205" t="inlineStr">
         <is>
           <t>L8</t>
         </is>

--- a/data/nzd0114/nzd0114.xlsx
+++ b/data/nzd0114/nzd0114.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN205"/>
+  <dimension ref="A1:AN206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25994,7 +25994,7 @@
         <v>312.93</v>
       </c>
       <c r="X205" t="n">
-        <v>365.96</v>
+        <v>345.38</v>
       </c>
       <c r="Y205" t="n">
         <v>355</v>
@@ -26042,6 +26042,132 @@
         <v>192.71</v>
       </c>
       <c r="AN205" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:04:44+00:00</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>290.79</v>
+      </c>
+      <c r="C206" t="n">
+        <v>285.67</v>
+      </c>
+      <c r="D206" t="n">
+        <v>283.19</v>
+      </c>
+      <c r="E206" t="n">
+        <v>282.97</v>
+      </c>
+      <c r="F206" t="n">
+        <v>289.21</v>
+      </c>
+      <c r="G206" t="n">
+        <v>284.31</v>
+      </c>
+      <c r="H206" t="n">
+        <v>281.93</v>
+      </c>
+      <c r="I206" t="n">
+        <v>279.02</v>
+      </c>
+      <c r="J206" t="n">
+        <v>279.64</v>
+      </c>
+      <c r="K206" t="n">
+        <v>284.52</v>
+      </c>
+      <c r="L206" t="n">
+        <v>291.28</v>
+      </c>
+      <c r="M206" t="n">
+        <v>297.85</v>
+      </c>
+      <c r="N206" t="n">
+        <v>327.85</v>
+      </c>
+      <c r="O206" t="n">
+        <v>319.03</v>
+      </c>
+      <c r="P206" t="n">
+        <v>313.12</v>
+      </c>
+      <c r="Q206" t="n">
+        <v>307.78</v>
+      </c>
+      <c r="R206" t="n">
+        <v>300.77</v>
+      </c>
+      <c r="S206" t="n">
+        <v>305.38</v>
+      </c>
+      <c r="T206" t="n">
+        <v>310.72</v>
+      </c>
+      <c r="U206" t="n">
+        <v>318.24</v>
+      </c>
+      <c r="V206" t="n">
+        <v>321.32</v>
+      </c>
+      <c r="W206" t="n">
+        <v>310.55</v>
+      </c>
+      <c r="X206" t="n">
+        <v>335.3</v>
+      </c>
+      <c r="Y206" t="n">
+        <v>345.61</v>
+      </c>
+      <c r="Z206" t="n">
+        <v>336.35</v>
+      </c>
+      <c r="AA206" t="n">
+        <v>325.73</v>
+      </c>
+      <c r="AB206" t="n">
+        <v>320.16</v>
+      </c>
+      <c r="AC206" t="n">
+        <v>313.7</v>
+      </c>
+      <c r="AD206" t="n">
+        <v>306.69</v>
+      </c>
+      <c r="AE206" t="n">
+        <v>304.35</v>
+      </c>
+      <c r="AF206" t="n">
+        <v>301.1</v>
+      </c>
+      <c r="AG206" t="n">
+        <v>300.02</v>
+      </c>
+      <c r="AH206" t="n">
+        <v>285.69</v>
+      </c>
+      <c r="AI206" t="n">
+        <v>268.59</v>
+      </c>
+      <c r="AJ206" t="n">
+        <v>246.31</v>
+      </c>
+      <c r="AK206" t="n">
+        <v>233.12</v>
+      </c>
+      <c r="AL206" t="n">
+        <v>245.52</v>
+      </c>
+      <c r="AM206" t="n">
+        <v>192.71</v>
+      </c>
+      <c r="AN206" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -26058,7 +26184,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B208"/>
+  <dimension ref="A1:B209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28141,6 +28267,16 @@
       </c>
       <c r="B208" t="n">
         <v>-0.58</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>0.26</v>
       </c>
     </row>
   </sheetData>
@@ -28309,28 +28445,28 @@
         <v>0.0582</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2566284607442066</v>
+        <v>0.2613479529179949</v>
       </c>
       <c r="J2" t="n">
+        <v>205</v>
+      </c>
+      <c r="K2" t="n">
         <v>204</v>
       </c>
-      <c r="K2" t="n">
-        <v>203</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.02606626527596334</v>
+        <v>0.0272647539609715</v>
       </c>
       <c r="M2" t="n">
-        <v>9.588752334360088</v>
+        <v>9.56668178332165</v>
       </c>
       <c r="N2" t="n">
-        <v>129.9134324315208</v>
+        <v>129.3876237244676</v>
       </c>
       <c r="O2" t="n">
-        <v>11.3979573797905</v>
+        <v>11.37486807503575</v>
       </c>
       <c r="P2" t="n">
-        <v>279.1532956176703</v>
+        <v>279.1013075387476</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -28387,28 +28523,28 @@
         <v>0.0562</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3855322269360137</v>
+        <v>0.3876870338402594</v>
       </c>
       <c r="J3" t="n">
+        <v>205</v>
+      </c>
+      <c r="K3" t="n">
         <v>204</v>
       </c>
-      <c r="K3" t="n">
-        <v>203</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.04622133707248166</v>
+        <v>0.04718294035374626</v>
       </c>
       <c r="M3" t="n">
-        <v>10.63691895929349</v>
+        <v>10.59442377122066</v>
       </c>
       <c r="N3" t="n">
-        <v>161.9273814739376</v>
+        <v>161.1567635971356</v>
       </c>
       <c r="O3" t="n">
-        <v>12.7250690164705</v>
+        <v>12.69475338859072</v>
       </c>
       <c r="P3" t="n">
-        <v>273.2085834631341</v>
+        <v>273.1848469535106</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -28465,28 +28601,28 @@
         <v>0.0536</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3391040250568816</v>
+        <v>0.3378669229745632</v>
       </c>
       <c r="J4" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K4" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03496620397708639</v>
+        <v>0.0350748950215134</v>
       </c>
       <c r="M4" t="n">
-        <v>10.77513162249473</v>
+        <v>10.72846987849597</v>
       </c>
       <c r="N4" t="n">
-        <v>168.0391082283922</v>
+        <v>167.2189970290253</v>
       </c>
       <c r="O4" t="n">
-        <v>12.96298994169139</v>
+        <v>12.93131845671683</v>
       </c>
       <c r="P4" t="n">
-        <v>275.4115974906641</v>
+        <v>275.4252226178945</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -28543,28 +28679,28 @@
         <v>0.0601</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2493250642253868</v>
+        <v>0.2430809800060053</v>
       </c>
       <c r="J5" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K5" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01879207879805067</v>
+        <v>0.01804738220044355</v>
       </c>
       <c r="M5" t="n">
-        <v>10.85638032277797</v>
+        <v>10.83485023329628</v>
       </c>
       <c r="N5" t="n">
-        <v>168.8134042579661</v>
+        <v>168.1720379034758</v>
       </c>
       <c r="O5" t="n">
-        <v>12.99282125860146</v>
+        <v>12.96811620488789</v>
       </c>
       <c r="P5" t="n">
-        <v>282.5835763925651</v>
+        <v>282.6530600160937</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -28621,28 +28757,28 @@
         <v>0.0604</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0663421046500139</v>
+        <v>0.06352798406084575</v>
       </c>
       <c r="J6" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K6" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001275340185808105</v>
+        <v>0.001181778456640248</v>
       </c>
       <c r="M6" t="n">
-        <v>11.33442036943741</v>
+        <v>11.29302580322518</v>
       </c>
       <c r="N6" t="n">
-        <v>179.6068062074049</v>
+        <v>178.7521114146828</v>
       </c>
       <c r="O6" t="n">
-        <v>13.40174638647534</v>
+        <v>13.36982091931985</v>
       </c>
       <c r="P6" t="n">
-        <v>290.2553703858799</v>
+        <v>290.2867565801232</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -28699,28 +28835,28 @@
         <v>0.0414</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3087661231735764</v>
+        <v>0.3021094928823964</v>
       </c>
       <c r="J7" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K7" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01931008165209525</v>
+        <v>0.01868216515966614</v>
       </c>
       <c r="M7" t="n">
-        <v>13.38314991959459</v>
+        <v>13.35086725590739</v>
       </c>
       <c r="N7" t="n">
-        <v>247.0427215832053</v>
+        <v>246.0241067071157</v>
       </c>
       <c r="O7" t="n">
-        <v>15.7175927413585</v>
+        <v>15.68515561628624</v>
       </c>
       <c r="P7" t="n">
-        <v>282.6382531796153</v>
+        <v>282.7133535599608</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -28777,28 +28913,28 @@
         <v>0.0535</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2061781020712798</v>
+        <v>0.2014176851189389</v>
       </c>
       <c r="J8" t="n">
+        <v>205</v>
+      </c>
+      <c r="K8" t="n">
         <v>204</v>
       </c>
-      <c r="K8" t="n">
-        <v>203</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.008748844712888726</v>
+        <v>0.008438131833700679</v>
       </c>
       <c r="M8" t="n">
-        <v>12.99768680475888</v>
+        <v>12.95899134426828</v>
       </c>
       <c r="N8" t="n">
-        <v>250.0571520584674</v>
+        <v>248.9415148616593</v>
       </c>
       <c r="O8" t="n">
-        <v>15.81319550433964</v>
+        <v>15.77788055670531</v>
       </c>
       <c r="P8" t="n">
-        <v>281.21124913192</v>
+        <v>281.2641900571757</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -28855,28 +28991,28 @@
         <v>0.0598</v>
       </c>
       <c r="I9" t="n">
-        <v>0.05978419711761183</v>
+        <v>0.05421552233446576</v>
       </c>
       <c r="J9" t="n">
+        <v>205</v>
+      </c>
+      <c r="K9" t="n">
         <v>204</v>
       </c>
-      <c r="K9" t="n">
-        <v>203</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.001071114697368092</v>
+        <v>0.0008897151119794389</v>
       </c>
       <c r="M9" t="n">
-        <v>10.99872269317829</v>
+        <v>10.96897360497909</v>
       </c>
       <c r="N9" t="n">
-        <v>173.0583674822135</v>
+        <v>172.360748591343</v>
       </c>
       <c r="O9" t="n">
-        <v>13.15516504959985</v>
+        <v>13.12862325574708</v>
       </c>
       <c r="P9" t="n">
-        <v>283.0179026816302</v>
+        <v>283.0798322979683</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -28933,28 +29069,28 @@
         <v>0.0436</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1706424925438497</v>
+        <v>-0.1751796104545591</v>
       </c>
       <c r="J10" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K10" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L10" t="n">
-        <v>0.00823359719283101</v>
+        <v>0.008761941223009773</v>
       </c>
       <c r="M10" t="n">
-        <v>10.98985282785205</v>
+        <v>10.9566986976179</v>
       </c>
       <c r="N10" t="n">
-        <v>178.5434068883175</v>
+        <v>177.76102629813</v>
       </c>
       <c r="O10" t="n">
-        <v>13.3620135791099</v>
+        <v>13.33270513804794</v>
       </c>
       <c r="P10" t="n">
-        <v>288.6610657847006</v>
+        <v>288.7121522022348</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -29011,28 +29147,28 @@
         <v>0.057</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.02064067212198165</v>
+        <v>-0.02404419567860988</v>
       </c>
       <c r="J11" t="n">
+        <v>205</v>
+      </c>
+      <c r="K11" t="n">
         <v>204</v>
       </c>
-      <c r="K11" t="n">
-        <v>203</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.000122356843401783</v>
+        <v>0.0001677594564789553</v>
       </c>
       <c r="M11" t="n">
-        <v>11.31951594760496</v>
+        <v>11.28026613854155</v>
       </c>
       <c r="N11" t="n">
-        <v>180.7538144202391</v>
+        <v>179.9240633582076</v>
       </c>
       <c r="O11" t="n">
-        <v>13.44447151881542</v>
+        <v>13.41357757491295</v>
       </c>
       <c r="P11" t="n">
-        <v>288.4889578858869</v>
+        <v>288.5268087061031</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -29089,28 +29225,28 @@
         <v>0.0868</v>
       </c>
       <c r="I12" t="n">
-        <v>0.002186084356372342</v>
+        <v>-0.002612109145549238</v>
       </c>
       <c r="J12" t="n">
+        <v>205</v>
+      </c>
+      <c r="K12" t="n">
         <v>204</v>
       </c>
-      <c r="K12" t="n">
-        <v>203</v>
-      </c>
       <c r="L12" t="n">
-        <v>1.120498349660437e-06</v>
+        <v>1.616147080274466e-06</v>
       </c>
       <c r="M12" t="n">
-        <v>12.53197545162541</v>
+        <v>12.49510215460264</v>
       </c>
       <c r="N12" t="n">
-        <v>221.4335039595509</v>
+        <v>220.4599336340417</v>
       </c>
       <c r="O12" t="n">
-        <v>14.88064192027854</v>
+        <v>14.84789323890907</v>
       </c>
       <c r="P12" t="n">
-        <v>296.0333776706408</v>
+        <v>296.08673871151</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -29167,28 +29303,28 @@
         <v>0.0509</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.03531087792140868</v>
+        <v>-0.04653192844860227</v>
       </c>
       <c r="J13" t="n">
+        <v>205</v>
+      </c>
+      <c r="K13" t="n">
         <v>204</v>
       </c>
-      <c r="K13" t="n">
-        <v>203</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.000244460318022055</v>
+        <v>0.0004280038247239659</v>
       </c>
       <c r="M13" t="n">
-        <v>13.14314231480186</v>
+        <v>13.13044895884098</v>
       </c>
       <c r="N13" t="n">
-        <v>264.7425117339615</v>
+        <v>264.0566750112409</v>
       </c>
       <c r="O13" t="n">
-        <v>16.27090998481528</v>
+        <v>16.24982076858822</v>
       </c>
       <c r="P13" t="n">
-        <v>310.0548836439439</v>
+        <v>310.1796737207792</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -29245,28 +29381,28 @@
         <v>0.0503</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.003893364910154917</v>
+        <v>-0.0009398677204168597</v>
       </c>
       <c r="J14" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K14" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L14" t="n">
-        <v>3.38594094595468e-06</v>
+        <v>1.993907851050025e-07</v>
       </c>
       <c r="M14" t="n">
-        <v>12.29011524926477</v>
+        <v>12.24596902496624</v>
       </c>
       <c r="N14" t="n">
-        <v>233.2651443910778</v>
+        <v>232.1530984531138</v>
       </c>
       <c r="O14" t="n">
-        <v>15.27302014635867</v>
+        <v>15.23657108581566</v>
       </c>
       <c r="P14" t="n">
-        <v>324.9927662714318</v>
+        <v>324.9598810604587</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -29323,28 +29459,28 @@
         <v>0.0624</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.08552527751644212</v>
+        <v>-0.08882391404901066</v>
       </c>
       <c r="J15" t="n">
+        <v>205</v>
+      </c>
+      <c r="K15" t="n">
         <v>204</v>
       </c>
-      <c r="K15" t="n">
-        <v>203</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.001890077462698203</v>
+        <v>0.002059695854113364</v>
       </c>
       <c r="M15" t="n">
-        <v>11.48263323519372</v>
+        <v>11.43854928435143</v>
       </c>
       <c r="N15" t="n">
-        <v>200.5436711486103</v>
+        <v>199.6134946168473</v>
       </c>
       <c r="O15" t="n">
-        <v>14.1613442564119</v>
+        <v>14.12846398646531</v>
       </c>
       <c r="P15" t="n">
-        <v>324.6199160893813</v>
+        <v>324.6566004537689</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -29401,28 +29537,28 @@
         <v>0.0615</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.08711226668543381</v>
+        <v>-0.08780477573806304</v>
       </c>
       <c r="J16" t="n">
+        <v>205</v>
+      </c>
+      <c r="K16" t="n">
         <v>204</v>
       </c>
-      <c r="K16" t="n">
-        <v>203</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.002110813652520083</v>
+        <v>0.002167399614966037</v>
       </c>
       <c r="M16" t="n">
-        <v>11.12593157700034</v>
+        <v>11.07446206612242</v>
       </c>
       <c r="N16" t="n">
-        <v>186.2568517276803</v>
+        <v>185.3461586051705</v>
       </c>
       <c r="O16" t="n">
-        <v>13.64759508952696</v>
+        <v>13.61418960515721</v>
       </c>
       <c r="P16" t="n">
-        <v>316.1403052901303</v>
+        <v>316.1480067310673</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -29479,28 +29615,28 @@
         <v>0.0573</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2477073955242607</v>
+        <v>-0.248782940689526</v>
       </c>
       <c r="J17" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K17" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L17" t="n">
-        <v>0.01415097448324121</v>
+        <v>0.01442284354942003</v>
       </c>
       <c r="M17" t="n">
-        <v>12.32464717981695</v>
+        <v>12.26842696119576</v>
       </c>
       <c r="N17" t="n">
-        <v>222.1380496463577</v>
+        <v>221.0494118457198</v>
       </c>
       <c r="O17" t="n">
-        <v>14.9042963485821</v>
+        <v>14.86773055465157</v>
       </c>
       <c r="P17" t="n">
-        <v>315.4643795017189</v>
+        <v>315.4763546073416</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -29557,28 +29693,28 @@
         <v>0.0537</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1489322869998546</v>
+        <v>-0.1558955737592066</v>
       </c>
       <c r="J18" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K18" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L18" t="n">
-        <v>0.005272122290299386</v>
+        <v>0.00582880761277027</v>
       </c>
       <c r="M18" t="n">
-        <v>12.14147799863262</v>
+        <v>12.10886797676307</v>
       </c>
       <c r="N18" t="n">
-        <v>217.7078715033763</v>
+        <v>216.867174296548</v>
       </c>
       <c r="O18" t="n">
-        <v>14.75492702467133</v>
+        <v>14.72641077440623</v>
       </c>
       <c r="P18" t="n">
-        <v>311.7141526852124</v>
+        <v>311.7917652120954</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -29635,28 +29771,28 @@
         <v>0.0545</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.03667094226820612</v>
+        <v>-0.0413668221616998</v>
       </c>
       <c r="J19" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K19" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0002817639062063781</v>
+        <v>0.0003622516894778993</v>
       </c>
       <c r="M19" t="n">
-        <v>12.76252143445991</v>
+        <v>12.71772216291412</v>
       </c>
       <c r="N19" t="n">
-        <v>242.8768173603351</v>
+        <v>241.7844408234365</v>
       </c>
       <c r="O19" t="n">
-        <v>15.5845056822581</v>
+        <v>15.54941930823902</v>
       </c>
       <c r="P19" t="n">
-        <v>310.9865746949033</v>
+        <v>311.0394487188212</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -29713,28 +29849,28 @@
         <v>0.0533</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.02615142817400212</v>
+        <v>-0.02898423697874754</v>
       </c>
       <c r="J20" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K20" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0001386751364667038</v>
+        <v>0.0001721682518833756</v>
       </c>
       <c r="M20" t="n">
-        <v>12.78684672764352</v>
+        <v>12.7359203298308</v>
       </c>
       <c r="N20" t="n">
-        <v>255.1571975032771</v>
+        <v>253.9386398548058</v>
       </c>
       <c r="O20" t="n">
-        <v>15.97364070909563</v>
+        <v>15.93545229526937</v>
       </c>
       <c r="P20" t="n">
-        <v>314.233561196846</v>
+        <v>314.2650719224123</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -29791,28 +29927,28 @@
         <v>0.0487</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1375133323413787</v>
+        <v>-0.1379452654790604</v>
       </c>
       <c r="J21" t="n">
+        <v>205</v>
+      </c>
+      <c r="K21" t="n">
         <v>204</v>
       </c>
-      <c r="K21" t="n">
-        <v>203</v>
-      </c>
       <c r="L21" t="n">
-        <v>0.004123236173786737</v>
+        <v>0.004193576824359835</v>
       </c>
       <c r="M21" t="n">
-        <v>12.43953577576492</v>
+        <v>12.38026414857078</v>
       </c>
       <c r="N21" t="n">
-        <v>236.1340672425361</v>
+        <v>234.9774476608182</v>
       </c>
       <c r="O21" t="n">
-        <v>15.3666543932808</v>
+        <v>15.32897412290915</v>
       </c>
       <c r="P21" t="n">
-        <v>322.3407827701752</v>
+        <v>322.3455967916458</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -29869,28 +30005,28 @@
         <v>0.0493</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2433086153314654</v>
+        <v>-0.2468921829571872</v>
       </c>
       <c r="J22" t="n">
+        <v>205</v>
+      </c>
+      <c r="K22" t="n">
         <v>204</v>
       </c>
-      <c r="K22" t="n">
-        <v>203</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.01210452219960056</v>
+        <v>0.0125887013469318</v>
       </c>
       <c r="M22" t="n">
-        <v>12.61964508214004</v>
+        <v>12.57288421103943</v>
       </c>
       <c r="N22" t="n">
-        <v>249.7928293964396</v>
+        <v>248.6303291382655</v>
       </c>
       <c r="O22" t="n">
-        <v>15.80483563332563</v>
+        <v>15.76801601782119</v>
       </c>
       <c r="P22" t="n">
-        <v>331.3924666891076</v>
+        <v>331.4324066010674</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -29947,28 +30083,28 @@
         <v>0.0539</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.4850674070010437</v>
+        <v>-0.5052061996406375</v>
       </c>
       <c r="J23" t="n">
+        <v>205</v>
+      </c>
+      <c r="K23" t="n">
         <v>204</v>
       </c>
-      <c r="K23" t="n">
-        <v>203</v>
-      </c>
       <c r="L23" t="n">
-        <v>0.04745044902028417</v>
+        <v>0.05139738597282906</v>
       </c>
       <c r="M23" t="n">
-        <v>12.7363049989509</v>
+        <v>12.76080377550266</v>
       </c>
       <c r="N23" t="n">
-        <v>244.2041754419427</v>
+        <v>244.9643535895075</v>
       </c>
       <c r="O23" t="n">
-        <v>15.62703348182062</v>
+        <v>15.65133711826269</v>
       </c>
       <c r="P23" t="n">
-        <v>343.6186144635152</v>
+        <v>343.8430672125664</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -30025,28 +30161,28 @@
         <v>0.0592</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.381686261197309</v>
+        <v>-0.409952021601897</v>
       </c>
       <c r="J24" t="n">
+        <v>205</v>
+      </c>
+      <c r="K24" t="n">
         <v>204</v>
       </c>
-      <c r="K24" t="n">
-        <v>203</v>
-      </c>
       <c r="L24" t="n">
-        <v>0.02962629657098825</v>
+        <v>0.03468641305536779</v>
       </c>
       <c r="M24" t="n">
-        <v>12.75603588414925</v>
+        <v>12.62373352889792</v>
       </c>
       <c r="N24" t="n">
-        <v>246.7040932706505</v>
+        <v>243.2189202064694</v>
       </c>
       <c r="O24" t="n">
-        <v>15.70681677714012</v>
+        <v>15.59547755621704</v>
       </c>
       <c r="P24" t="n">
-        <v>353.3314728458458</v>
+        <v>353.6456700872002</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -30103,28 +30239,28 @@
         <v>0.0698</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3248285452790581</v>
+        <v>-0.3360844052986944</v>
       </c>
       <c r="J25" t="n">
+        <v>205</v>
+      </c>
+      <c r="K25" t="n">
         <v>204</v>
       </c>
-      <c r="K25" t="n">
-        <v>203</v>
-      </c>
       <c r="L25" t="n">
-        <v>0.02473207896816398</v>
+        <v>0.02663285761605461</v>
       </c>
       <c r="M25" t="n">
-        <v>11.8933147031108</v>
+        <v>11.88431917051859</v>
       </c>
       <c r="N25" t="n">
-        <v>215.116308246274</v>
+        <v>214.6732348754376</v>
       </c>
       <c r="O25" t="n">
-        <v>14.6668438406589</v>
+        <v>14.65173146339495</v>
       </c>
       <c r="P25" t="n">
-        <v>365.5277323199844</v>
+        <v>365.6531821803387</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -30181,28 +30317,28 @@
         <v>0.0737</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4546979610148866</v>
+        <v>-0.4657829958574163</v>
       </c>
       <c r="J26" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K26" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L26" t="n">
-        <v>0.04069722674447374</v>
+        <v>0.04296115422222635</v>
       </c>
       <c r="M26" t="n">
-        <v>12.82032092770466</v>
+        <v>12.8040741042534</v>
       </c>
       <c r="N26" t="n">
-        <v>252.5613777721994</v>
+        <v>251.9129607305886</v>
       </c>
       <c r="O26" t="n">
-        <v>15.89217976780402</v>
+        <v>15.87176615032456</v>
       </c>
       <c r="P26" t="n">
-        <v>359.553529981795</v>
+        <v>359.6771027550967</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -30259,28 +30395,28 @@
         <v>0.0769</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.5694122046652133</v>
+        <v>-0.5816911301638492</v>
       </c>
       <c r="J27" t="n">
+        <v>205</v>
+      </c>
+      <c r="K27" t="n">
         <v>204</v>
       </c>
-      <c r="K27" t="n">
-        <v>203</v>
-      </c>
       <c r="L27" t="n">
-        <v>0.05558172677073958</v>
+        <v>0.05831065671202695</v>
       </c>
       <c r="M27" t="n">
-        <v>13.16827780688675</v>
+        <v>13.15319038691482</v>
       </c>
       <c r="N27" t="n">
-        <v>284.8311847415212</v>
+        <v>284.1625687403998</v>
       </c>
       <c r="O27" t="n">
-        <v>16.87694239906984</v>
+        <v>16.85712219628249</v>
       </c>
       <c r="P27" t="n">
-        <v>353.1836836745025</v>
+        <v>353.3205358996029</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -30337,28 +30473,28 @@
         <v>0.09089999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.6362338658697668</v>
+        <v>-0.6467909466088823</v>
       </c>
       <c r="J28" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K28" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L28" t="n">
-        <v>0.05887304358475909</v>
+        <v>0.06124329534285455</v>
       </c>
       <c r="M28" t="n">
-        <v>14.30379966139752</v>
+        <v>14.28406242565624</v>
       </c>
       <c r="N28" t="n">
-        <v>334.8539927173409</v>
+        <v>333.7438698273434</v>
       </c>
       <c r="O28" t="n">
-        <v>18.29901616801682</v>
+        <v>18.26865812881021</v>
       </c>
       <c r="P28" t="n">
-        <v>347.6622374981317</v>
+        <v>347.7800377673743</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -30415,28 +30551,28 @@
         <v>0.0786</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.5681194582773459</v>
+        <v>-0.5815772520226484</v>
       </c>
       <c r="J29" t="n">
+        <v>205</v>
+      </c>
+      <c r="K29" t="n">
         <v>204</v>
       </c>
-      <c r="K29" t="n">
-        <v>203</v>
-      </c>
       <c r="L29" t="n">
-        <v>0.05756403317782022</v>
+        <v>0.06057451425260363</v>
       </c>
       <c r="M29" t="n">
-        <v>13.40031699304821</v>
+        <v>13.39938189780904</v>
       </c>
       <c r="N29" t="n">
-        <v>278.7516010260463</v>
+        <v>278.2870381913415</v>
       </c>
       <c r="O29" t="n">
-        <v>16.69585580394267</v>
+        <v>16.6819374831385</v>
       </c>
       <c r="P29" t="n">
-        <v>342.5131905790034</v>
+        <v>342.661516662301</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -30493,28 +30629,28 @@
         <v>0.0825</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.6772580204645158</v>
+        <v>-0.6925863502879296</v>
       </c>
       <c r="J30" t="n">
+        <v>205</v>
+      </c>
+      <c r="K30" t="n">
         <v>204</v>
       </c>
-      <c r="K30" t="n">
-        <v>203</v>
-      </c>
       <c r="L30" t="n">
-        <v>0.07179640157211875</v>
+        <v>0.07531451238540121</v>
       </c>
       <c r="M30" t="n">
-        <v>13.9911215331918</v>
+        <v>13.99931064740604</v>
       </c>
       <c r="N30" t="n">
-        <v>311.2225755387255</v>
+        <v>310.8586993940885</v>
       </c>
       <c r="O30" t="n">
-        <v>17.64150151032291</v>
+        <v>17.63118542225929</v>
       </c>
       <c r="P30" t="n">
-        <v>340.2573626066991</v>
+        <v>340.4268261774859</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -30571,28 +30707,28 @@
         <v>0.06809999999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.7670719655147789</v>
+        <v>-0.7803711429296998</v>
       </c>
       <c r="J31" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K31" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L31" t="n">
-        <v>0.07538132043228019</v>
+        <v>0.07840527405805942</v>
       </c>
       <c r="M31" t="n">
-        <v>15.67788127473864</v>
+        <v>15.66714110407027</v>
       </c>
       <c r="N31" t="n">
-        <v>379.6307268671438</v>
+        <v>378.6232866792434</v>
       </c>
       <c r="O31" t="n">
-        <v>19.48411473142015</v>
+        <v>19.45824469676655</v>
       </c>
       <c r="P31" t="n">
-        <v>338.209933262935</v>
+        <v>338.3575072968034</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -30649,28 +30785,28 @@
         <v>0.1625</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.65867022208362</v>
+        <v>-0.673329320474512</v>
       </c>
       <c r="J32" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K32" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L32" t="n">
-        <v>0.05207825723276849</v>
+        <v>0.05470606386905685</v>
       </c>
       <c r="M32" t="n">
-        <v>16.63900804272199</v>
+        <v>16.62418598555341</v>
       </c>
       <c r="N32" t="n">
-        <v>411.8884305719866</v>
+        <v>410.8797160609668</v>
       </c>
       <c r="O32" t="n">
-        <v>20.29503462849932</v>
+        <v>20.27016813104832</v>
       </c>
       <c r="P32" t="n">
-        <v>333.2972852026589</v>
+        <v>333.4612944848856</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -30727,28 +30863,28 @@
         <v>0.0556</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.7511103497121921</v>
+        <v>-0.7625438189017202</v>
       </c>
       <c r="J33" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K33" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L33" t="n">
-        <v>0.06023442408557134</v>
+        <v>0.0625263724842221</v>
       </c>
       <c r="M33" t="n">
-        <v>16.70593804043617</v>
+        <v>16.67439527180557</v>
       </c>
       <c r="N33" t="n">
-        <v>456.8857784025836</v>
+        <v>455.1872661793098</v>
       </c>
       <c r="O33" t="n">
-        <v>21.37488662899955</v>
+        <v>21.33511814308301</v>
       </c>
       <c r="P33" t="n">
-        <v>331.1883196604969</v>
+        <v>331.3158801638567</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -30805,28 +30941,28 @@
         <v>0.0582</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.22806674179213</v>
+        <v>-1.241065802262577</v>
       </c>
       <c r="J34" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K34" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L34" t="n">
-        <v>0.1079376765511063</v>
+        <v>0.1109368138219012</v>
       </c>
       <c r="M34" t="n">
-        <v>20.25874494413302</v>
+        <v>20.22516142730645</v>
       </c>
       <c r="N34" t="n">
-        <v>646.39639062933</v>
+        <v>643.9317244305174</v>
       </c>
       <c r="O34" t="n">
-        <v>25.4243267487918</v>
+        <v>25.37580982807282</v>
       </c>
       <c r="P34" t="n">
-        <v>331.1116326874737</v>
+        <v>331.2564841646334</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
@@ -30883,28 +31019,28 @@
         <v>0.0295</v>
       </c>
       <c r="I35" t="n">
-        <v>-2.300225703813685</v>
+        <v>-2.306909833790106</v>
       </c>
       <c r="J35" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K35" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L35" t="n">
-        <v>0.1945884580219547</v>
+        <v>0.1971840488378529</v>
       </c>
       <c r="M35" t="n">
-        <v>26.41569842612146</v>
+        <v>26.31466308010825</v>
       </c>
       <c r="N35" t="n">
-        <v>1129.406924922723</v>
+        <v>1123.972061023222</v>
       </c>
       <c r="O35" t="n">
-        <v>33.60665001041792</v>
+        <v>33.52569255098576</v>
       </c>
       <c r="P35" t="n">
-        <v>336.4652281575629</v>
+        <v>336.5399746180988</v>
       </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
@@ -30961,28 +31097,28 @@
         <v>0.0326</v>
       </c>
       <c r="I36" t="n">
-        <v>-3.585918941232686</v>
+        <v>-3.590746011265877</v>
       </c>
       <c r="J36" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K36" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L36" t="n">
-        <v>0.2342896517517425</v>
+        <v>0.2368162120836074</v>
       </c>
       <c r="M36" t="n">
-        <v>37.85509639120802</v>
+        <v>37.68539491168868</v>
       </c>
       <c r="N36" t="n">
-        <v>2182.789989835114</v>
+        <v>2171.527596982173</v>
       </c>
       <c r="O36" t="n">
-        <v>46.72033807492316</v>
+        <v>46.59965232683794</v>
       </c>
       <c r="P36" t="n">
-        <v>346.4557198414693</v>
+        <v>346.5093393595106</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -31043,28 +31179,28 @@
         <v>0.0211</v>
       </c>
       <c r="I37" t="n">
-        <v>-6.465579479790306</v>
+        <v>-6.440037478408696</v>
       </c>
       <c r="J37" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K37" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L37" t="n">
-        <v>0.3600183510498666</v>
+        <v>0.3606086890086527</v>
       </c>
       <c r="M37" t="n">
-        <v>50.40484643148691</v>
+        <v>50.23738436904721</v>
       </c>
       <c r="N37" t="n">
-        <v>3777.871424728076</v>
+        <v>3761.038225412707</v>
       </c>
       <c r="O37" t="n">
-        <v>61.46439151840744</v>
+        <v>61.32730407748825</v>
       </c>
       <c r="P37" t="n">
-        <v>381.5460622228879</v>
+        <v>381.2568954606054</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -31125,28 +31261,28 @@
         <v>0.0218</v>
       </c>
       <c r="I38" t="n">
-        <v>-2.114060391723123</v>
+        <v>-2.148731335642212</v>
       </c>
       <c r="J38" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K38" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L38" t="n">
-        <v>0.2345290621381968</v>
+        <v>0.2412666604197352</v>
       </c>
       <c r="M38" t="n">
-        <v>22.19994949278469</v>
+        <v>22.21619691880679</v>
       </c>
       <c r="N38" t="n">
-        <v>755.1932614792382</v>
+        <v>756.4794107783033</v>
       </c>
       <c r="O38" t="n">
-        <v>27.48077985573259</v>
+        <v>27.50417078877862</v>
       </c>
       <c r="P38" t="n">
-        <v>333.6967966015841</v>
+        <v>334.0827901985942</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -31207,28 +31343,28 @@
         <v>0.0271</v>
       </c>
       <c r="I39" t="n">
-        <v>-3.183839795644183</v>
+        <v>-3.277906036221545</v>
       </c>
       <c r="J39" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K39" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L39" t="n">
-        <v>0.2915668679860686</v>
+        <v>0.2995740840898071</v>
       </c>
       <c r="M39" t="n">
-        <v>25.69408727583397</v>
+        <v>25.99999098139935</v>
       </c>
       <c r="N39" t="n">
-        <v>1215.997415206414</v>
+        <v>1247.618790068113</v>
       </c>
       <c r="O39" t="n">
-        <v>34.87115448628585</v>
+        <v>35.32164761259182</v>
       </c>
       <c r="P39" t="n">
-        <v>361.7797935506713</v>
+        <v>362.8747161364636</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -31270,7 +31406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN205"/>
+  <dimension ref="A1:AN206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72019,7 +72155,7 @@
       </c>
       <c r="X205" t="inlineStr">
         <is>
-          <t>-36.13195092261952,175.4251687335748</t>
+          <t>-36.131993713923585,175.42494631277415</t>
         </is>
       </c>
       <c r="Y205" t="inlineStr">
@@ -72098,6 +72234,208 @@
         </is>
       </c>
       <c r="AN205" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:04:44+00:00</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>-36.116228466366415,175.4250036878046</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>-36.11687909561834,175.4245998674277</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>-36.117538648669054,175.42422322028898</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>-36.11820584033504,175.4238698355634</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>-36.11893870801955,175.4235622059686</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>-36.119712249314404,175.42325444459354</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>-36.12047275213766,175.42310345266424</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>-36.12118933031786,175.4229551626881</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>-36.121909498125675,175.4228458249024</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>-36.12263399929594,175.4227834958412</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>-36.12336040916237,175.42274191354218</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>-36.12408661887669,175.42269823595083</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>-36.124872916444964,175.42290946226603</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>-36.125651852485035,175.42291634959614</t>
+        </is>
+      </c>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>-36.12639240976276,175.42305058316768</t>
+        </is>
+      </c>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>-36.12711208224529,175.42318625818203</t>
+        </is>
+      </c>
+      <c r="R206" t="inlineStr">
+        <is>
+          <t>-36.127835220602144,175.42330388433797</t>
+        </is>
+      </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>-36.12853419306073,175.423547088764</t>
+        </is>
+      </c>
+      <c r="T206" t="inlineStr">
+        <is>
+          <t>-36.12923164118242,175.42379818333953</t>
+        </is>
+      </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>-36.129924550102416,175.4240728389407</t>
+        </is>
+      </c>
+      <c r="V206" t="inlineStr">
+        <is>
+          <t>-36.13062668404739,175.42429951079149</t>
+        </is>
+      </c>
+      <c r="W206" t="inlineStr">
+        <is>
+          <t>-36.13135760864504,175.42437649862458</t>
+        </is>
+      </c>
+      <c r="X206" t="inlineStr">
+        <is>
+          <t>-36.132014672782056,175.4248373718774</t>
+        </is>
+      </c>
+      <c r="Y206" t="inlineStr">
+        <is>
+          <t>-36.13272127568517,175.42514886655283</t>
+        </is>
+      </c>
+      <c r="Z206" t="inlineStr">
+        <is>
+          <t>-36.133417655282386,175.42550037795135</t>
+        </is>
+      </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>-36.13409983422505,175.42583753138084</t>
+        </is>
+      </c>
+      <c r="AB206" t="inlineStr">
+        <is>
+          <t>-36.13475820446611,175.42622253501636</t>
+        </is>
+      </c>
+      <c r="AC206" t="inlineStr">
+        <is>
+          <t>-36.135420593074286,175.42659898613084</t>
+        </is>
+      </c>
+      <c r="AD206" t="inlineStr">
+        <is>
+          <t>-36.136085463128836,175.426970151573</t>
+        </is>
+      </c>
+      <c r="AE206" t="inlineStr">
+        <is>
+          <t>-36.136729217517654,175.42738618994085</t>
+        </is>
+      </c>
+      <c r="AF206" t="inlineStr">
+        <is>
+          <t>-36.137382921592625,175.42779766801303</t>
+        </is>
+      </c>
+      <c r="AG206" t="inlineStr">
+        <is>
+          <t>-36.138028451447525,175.42825765642053</t>
+        </is>
+      </c>
+      <c r="AH206" t="inlineStr">
+        <is>
+          <t>-36.1387180944896,175.42862762446526</t>
+        </is>
+      </c>
+      <c r="AI206" t="inlineStr">
+        <is>
+          <t>-36.139411088124184,175.42896351586933</t>
+        </is>
+      </c>
+      <c r="AJ206" t="inlineStr">
+        <is>
+          <t>-36.140130298048405,175.42925180127853</t>
+        </is>
+      </c>
+      <c r="AK206" t="inlineStr">
+        <is>
+          <t>-36.140803491876724,175.4296236215357</t>
+        </is>
+      </c>
+      <c r="AL206" t="inlineStr">
+        <is>
+          <t>-36.141347148162026,175.43023061465408</t>
+        </is>
+      </c>
+      <c r="AM206" t="inlineStr">
+        <is>
+          <t>-36.14222088527489,175.43023831966212</t>
+        </is>
+      </c>
+      <c r="AN206" t="inlineStr">
         <is>
           <t>L8</t>
         </is>

--- a/data/nzd0114/nzd0114.xlsx
+++ b/data/nzd0114/nzd0114.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN206"/>
+  <dimension ref="A1:AN208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25789,7 +25789,7 @@
         <v>262.7</v>
       </c>
       <c r="AM203" t="n">
-        <v>263.5</v>
+        <v>306.53</v>
       </c>
       <c r="AN203" t="inlineStr">
         <is>
@@ -25912,9 +25912,7 @@
       <c r="AL204" t="n">
         <v>258.38</v>
       </c>
-      <c r="AM204" t="n">
-        <v>220.46</v>
-      </c>
+      <c r="AM204" t="inlineStr"/>
       <c r="AN204" t="inlineStr">
         <is>
           <t>L8</t>
@@ -26038,9 +26036,7 @@
       <c r="AL205" t="n">
         <v>245.52</v>
       </c>
-      <c r="AM205" t="n">
-        <v>192.71</v>
-      </c>
+      <c r="AM205" t="inlineStr"/>
       <c r="AN205" t="inlineStr">
         <is>
           <t>L8</t>
@@ -26164,12 +26160,262 @@
       <c r="AL206" t="n">
         <v>245.52</v>
       </c>
-      <c r="AM206" t="n">
-        <v>192.71</v>
-      </c>
+      <c r="AM206" t="inlineStr"/>
       <c r="AN206" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:04:54+00:00</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>288.04</v>
+      </c>
+      <c r="C207" t="n">
+        <v>283.35</v>
+      </c>
+      <c r="D207" t="n">
+        <v>281.95</v>
+      </c>
+      <c r="E207" t="n">
+        <v>281.71</v>
+      </c>
+      <c r="F207" t="n">
+        <v>289.78</v>
+      </c>
+      <c r="G207" t="n">
+        <v>284.85</v>
+      </c>
+      <c r="H207" t="n">
+        <v>282.97</v>
+      </c>
+      <c r="I207" t="n">
+        <v>280.16</v>
+      </c>
+      <c r="J207" t="n">
+        <v>277.69</v>
+      </c>
+      <c r="K207" t="n">
+        <v>285.11</v>
+      </c>
+      <c r="L207" t="n">
+        <v>293.14</v>
+      </c>
+      <c r="M207" t="n">
+        <v>300.19</v>
+      </c>
+      <c r="N207" t="n">
+        <v>326.99</v>
+      </c>
+      <c r="O207" t="n">
+        <v>317.6</v>
+      </c>
+      <c r="P207" t="n">
+        <v>310.51</v>
+      </c>
+      <c r="Q207" t="n">
+        <v>306.56</v>
+      </c>
+      <c r="R207" t="n">
+        <v>300.77</v>
+      </c>
+      <c r="S207" t="n">
+        <v>303.64</v>
+      </c>
+      <c r="T207" t="n">
+        <v>306.83</v>
+      </c>
+      <c r="U207" t="n">
+        <v>313.8</v>
+      </c>
+      <c r="V207" t="n">
+        <v>318.21</v>
+      </c>
+      <c r="W207" t="n">
+        <v>311.31</v>
+      </c>
+      <c r="X207" t="n">
+        <v>335.28</v>
+      </c>
+      <c r="Y207" t="n">
+        <v>344.55</v>
+      </c>
+      <c r="Z207" t="n">
+        <v>335.64</v>
+      </c>
+      <c r="AA207" t="n">
+        <v>324.59</v>
+      </c>
+      <c r="AB207" t="n">
+        <v>322.31</v>
+      </c>
+      <c r="AC207" t="n">
+        <v>317.06</v>
+      </c>
+      <c r="AD207" t="n">
+        <v>306.3</v>
+      </c>
+      <c r="AE207" t="n">
+        <v>305.25</v>
+      </c>
+      <c r="AF207" t="n">
+        <v>307.2</v>
+      </c>
+      <c r="AG207" t="n">
+        <v>298.36</v>
+      </c>
+      <c r="AH207" t="n">
+        <v>282.26</v>
+      </c>
+      <c r="AI207" t="n">
+        <v>267.55</v>
+      </c>
+      <c r="AJ207" t="n">
+        <v>253.21</v>
+      </c>
+      <c r="AK207" t="n">
+        <v>238.43</v>
+      </c>
+      <c r="AL207" t="n">
+        <v>245.52</v>
+      </c>
+      <c r="AM207" t="n">
+        <v>313.45</v>
+      </c>
+      <c r="AN207" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:06+00:00</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>283.73</v>
+      </c>
+      <c r="C208" t="n">
+        <v>279.1</v>
+      </c>
+      <c r="D208" t="n">
+        <v>279.31</v>
+      </c>
+      <c r="E208" t="n">
+        <v>279.35</v>
+      </c>
+      <c r="F208" t="n">
+        <v>286.55</v>
+      </c>
+      <c r="G208" t="n">
+        <v>282.69</v>
+      </c>
+      <c r="H208" t="n">
+        <v>280.27</v>
+      </c>
+      <c r="I208" t="n">
+        <v>279.16</v>
+      </c>
+      <c r="J208" t="n">
+        <v>274.34</v>
+      </c>
+      <c r="K208" t="n">
+        <v>282.31</v>
+      </c>
+      <c r="L208" t="n">
+        <v>291.99</v>
+      </c>
+      <c r="M208" t="n">
+        <v>298.31</v>
+      </c>
+      <c r="N208" t="n">
+        <v>321.82</v>
+      </c>
+      <c r="O208" t="n">
+        <v>314.53</v>
+      </c>
+      <c r="P208" t="n">
+        <v>308.08</v>
+      </c>
+      <c r="Q208" t="n">
+        <v>303.81</v>
+      </c>
+      <c r="R208" t="n">
+        <v>298.42</v>
+      </c>
+      <c r="S208" t="n">
+        <v>301.04</v>
+      </c>
+      <c r="T208" t="n">
+        <v>302.17</v>
+      </c>
+      <c r="U208" t="n">
+        <v>309.35</v>
+      </c>
+      <c r="V208" t="n">
+        <v>314.05</v>
+      </c>
+      <c r="W208" t="n">
+        <v>309.39</v>
+      </c>
+      <c r="X208" t="n">
+        <v>331.96</v>
+      </c>
+      <c r="Y208" t="n">
+        <v>341.3</v>
+      </c>
+      <c r="Z208" t="n">
+        <v>335.64</v>
+      </c>
+      <c r="AA208" t="n">
+        <v>324.59</v>
+      </c>
+      <c r="AB208" t="n">
+        <v>322.31</v>
+      </c>
+      <c r="AC208" t="n">
+        <v>317.06</v>
+      </c>
+      <c r="AD208" t="n">
+        <v>306.3</v>
+      </c>
+      <c r="AE208" t="n">
+        <v>305.25</v>
+      </c>
+      <c r="AF208" t="n">
+        <v>307.2</v>
+      </c>
+      <c r="AG208" t="n">
+        <v>298.36</v>
+      </c>
+      <c r="AH208" t="n">
+        <v>282.26</v>
+      </c>
+      <c r="AI208" t="n">
+        <v>267.55</v>
+      </c>
+      <c r="AJ208" t="n">
+        <v>253.21</v>
+      </c>
+      <c r="AK208" t="n">
+        <v>238.43</v>
+      </c>
+      <c r="AL208" t="n">
+        <v>245.52</v>
+      </c>
+      <c r="AM208" t="n">
+        <v>305.85</v>
+      </c>
+      <c r="AN208" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -26184,7 +26430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B209"/>
+  <dimension ref="A1:B211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28277,6 +28523,26 @@
       </c>
       <c r="B209" t="n">
         <v>0.26</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>-0.7</v>
       </c>
     </row>
   </sheetData>
@@ -28445,28 +28711,28 @@
         <v>0.0582</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2613479529179949</v>
+        <v>0.2609437107435971</v>
       </c>
       <c r="J2" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K2" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0272647539609715</v>
+        <v>0.02773121429786352</v>
       </c>
       <c r="M2" t="n">
-        <v>9.56668178332165</v>
+        <v>9.494658019968433</v>
       </c>
       <c r="N2" t="n">
-        <v>129.3876237244676</v>
+        <v>128.1771583988785</v>
       </c>
       <c r="O2" t="n">
-        <v>11.37486807503575</v>
+        <v>11.32153516087277</v>
       </c>
       <c r="P2" t="n">
-        <v>279.1013075387476</v>
+        <v>279.1058201058885</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -28523,28 +28789,28 @@
         <v>0.0562</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3876870338402594</v>
+        <v>0.3832045547708742</v>
       </c>
       <c r="J3" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K3" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04718294035374626</v>
+        <v>0.04705011582797602</v>
       </c>
       <c r="M3" t="n">
-        <v>10.59442377122066</v>
+        <v>10.51568520910221</v>
       </c>
       <c r="N3" t="n">
-        <v>161.1567635971356</v>
+        <v>159.6872363705048</v>
       </c>
       <c r="O3" t="n">
-        <v>12.69475338859072</v>
+        <v>12.63674152503345</v>
       </c>
       <c r="P3" t="n">
-        <v>273.1848469535106</v>
+        <v>273.2344488747902</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -28601,28 +28867,28 @@
         <v>0.0536</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3378669229745632</v>
+        <v>0.3304904130280304</v>
       </c>
       <c r="J4" t="n">
+        <v>207</v>
+      </c>
+      <c r="K4" t="n">
         <v>205</v>
       </c>
-      <c r="K4" t="n">
-        <v>203</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.0350748950215134</v>
+        <v>0.03426360536894901</v>
       </c>
       <c r="M4" t="n">
-        <v>10.72846987849597</v>
+        <v>10.66137205819977</v>
       </c>
       <c r="N4" t="n">
-        <v>167.2189970290253</v>
+        <v>165.7436350450536</v>
       </c>
       <c r="O4" t="n">
-        <v>12.93131845671683</v>
+        <v>12.8741459928437</v>
       </c>
       <c r="P4" t="n">
-        <v>275.4252226178945</v>
+        <v>275.5067940757752</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -28679,28 +28945,28 @@
         <v>0.0601</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2430809800060053</v>
+        <v>0.2262672023901728</v>
       </c>
       <c r="J5" t="n">
+        <v>207</v>
+      </c>
+      <c r="K5" t="n">
         <v>205</v>
       </c>
-      <c r="K5" t="n">
-        <v>203</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.01804738220044355</v>
+        <v>0.01593512651811435</v>
       </c>
       <c r="M5" t="n">
-        <v>10.83485023329628</v>
+        <v>10.81379770357142</v>
       </c>
       <c r="N5" t="n">
-        <v>168.1720379034758</v>
+        <v>167.2484092987666</v>
       </c>
       <c r="O5" t="n">
-        <v>12.96811620488789</v>
+        <v>12.93245565616858</v>
       </c>
       <c r="P5" t="n">
-        <v>282.6530600160937</v>
+        <v>282.8408681325</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -28757,28 +29023,28 @@
         <v>0.0604</v>
       </c>
       <c r="I6" t="n">
-        <v>0.06352798406084575</v>
+        <v>0.0560626818032977</v>
       </c>
       <c r="J6" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K6" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001181778456640248</v>
+        <v>0.0009391815007723237</v>
       </c>
       <c r="M6" t="n">
-        <v>11.29302580322518</v>
+        <v>11.22080759622482</v>
       </c>
       <c r="N6" t="n">
-        <v>178.7521114146828</v>
+        <v>177.1560389715528</v>
       </c>
       <c r="O6" t="n">
-        <v>13.36982091931985</v>
+        <v>13.30999770742102</v>
       </c>
       <c r="P6" t="n">
-        <v>290.2867565801232</v>
+        <v>290.3703581327941</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -28835,28 +29101,28 @@
         <v>0.0414</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3021094928823964</v>
+        <v>0.2881618109472234</v>
       </c>
       <c r="J7" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K7" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01868216515966614</v>
+        <v>0.01735015801106554</v>
       </c>
       <c r="M7" t="n">
-        <v>13.35086725590739</v>
+        <v>13.28991230879227</v>
       </c>
       <c r="N7" t="n">
-        <v>246.0241067071157</v>
+        <v>244.083049336671</v>
       </c>
       <c r="O7" t="n">
-        <v>15.68515561628624</v>
+        <v>15.62315747013615</v>
       </c>
       <c r="P7" t="n">
-        <v>282.7133535599608</v>
+        <v>282.871301213511</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -28913,28 +29179,28 @@
         <v>0.0535</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2014176851189389</v>
+        <v>0.1916099535126202</v>
       </c>
       <c r="J8" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K8" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L8" t="n">
-        <v>0.008438131833700679</v>
+        <v>0.007795975120671095</v>
       </c>
       <c r="M8" t="n">
-        <v>12.95899134426828</v>
+        <v>12.88383544395669</v>
       </c>
       <c r="N8" t="n">
-        <v>248.9415148616593</v>
+        <v>246.7806660841539</v>
       </c>
       <c r="O8" t="n">
-        <v>15.77788055670531</v>
+        <v>15.70925415429243</v>
       </c>
       <c r="P8" t="n">
-        <v>281.2641900571757</v>
+        <v>281.3736846006834</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -28991,28 +29257,28 @@
         <v>0.0598</v>
       </c>
       <c r="I9" t="n">
-        <v>0.05421552233446576</v>
+        <v>0.04473375993657817</v>
       </c>
       <c r="J9" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K9" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0008897151119794389</v>
+        <v>0.0006179775123663633</v>
       </c>
       <c r="M9" t="n">
-        <v>10.96897360497909</v>
+        <v>10.90328296835194</v>
       </c>
       <c r="N9" t="n">
-        <v>172.360748591343</v>
+        <v>170.9126184167899</v>
       </c>
       <c r="O9" t="n">
-        <v>13.12862325574708</v>
+        <v>13.07335528534239</v>
       </c>
       <c r="P9" t="n">
-        <v>283.0798322979683</v>
+        <v>283.1856714822922</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -29069,28 +29335,28 @@
         <v>0.0436</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1751796104545591</v>
+        <v>-0.1910628614226563</v>
       </c>
       <c r="J10" t="n">
+        <v>207</v>
+      </c>
+      <c r="K10" t="n">
         <v>205</v>
       </c>
-      <c r="K10" t="n">
-        <v>203</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.008761941223009773</v>
+        <v>0.01058921752076136</v>
       </c>
       <c r="M10" t="n">
-        <v>10.9566986976179</v>
+        <v>10.92198117446265</v>
       </c>
       <c r="N10" t="n">
-        <v>177.76102629813</v>
+        <v>176.6609269630143</v>
       </c>
       <c r="O10" t="n">
-        <v>13.33270513804794</v>
+        <v>13.29138544181961</v>
       </c>
       <c r="P10" t="n">
-        <v>288.7121522022348</v>
+        <v>288.8916626252537</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -29147,28 +29413,28 @@
         <v>0.057</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.02404419567860988</v>
+        <v>-0.03218521765909099</v>
       </c>
       <c r="J11" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K11" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0001677594564789553</v>
+        <v>0.0003066380762505316</v>
       </c>
       <c r="M11" t="n">
-        <v>11.28026613854155</v>
+        <v>11.20888062010625</v>
       </c>
       <c r="N11" t="n">
-        <v>179.9240633582076</v>
+        <v>178.3602567383257</v>
       </c>
       <c r="O11" t="n">
-        <v>13.41357757491295</v>
+        <v>13.35515843179427</v>
       </c>
       <c r="P11" t="n">
-        <v>288.5268087061031</v>
+        <v>288.6177013802629</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -29225,28 +29491,28 @@
         <v>0.0868</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.002612109145549238</v>
+        <v>-0.009333482845386386</v>
       </c>
       <c r="J12" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K12" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L12" t="n">
-        <v>1.616147080274466e-06</v>
+        <v>2.106207333618659e-05</v>
       </c>
       <c r="M12" t="n">
-        <v>12.49510215460264</v>
+        <v>12.40759184047133</v>
       </c>
       <c r="N12" t="n">
-        <v>220.4599336340417</v>
+        <v>218.4347150933684</v>
       </c>
       <c r="O12" t="n">
-        <v>14.84789323890907</v>
+        <v>14.7795370392096</v>
       </c>
       <c r="P12" t="n">
-        <v>296.08673871151</v>
+        <v>296.1617697747788</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -29303,28 +29569,28 @@
         <v>0.0509</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.04653192844860227</v>
+        <v>-0.0654046611124976</v>
       </c>
       <c r="J13" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K13" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0004280038247239659</v>
+        <v>0.0008603001676731337</v>
       </c>
       <c r="M13" t="n">
-        <v>13.13044895884098</v>
+        <v>13.08844737354709</v>
       </c>
       <c r="N13" t="n">
-        <v>264.0566750112409</v>
+        <v>262.384435083301</v>
       </c>
       <c r="O13" t="n">
-        <v>16.24982076858822</v>
+        <v>16.1982849426506</v>
       </c>
       <c r="P13" t="n">
-        <v>310.1796737207792</v>
+        <v>310.3903374612598</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -29381,28 +29647,28 @@
         <v>0.0503</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.0009398677204168597</v>
+        <v>-0.001979171922324094</v>
       </c>
       <c r="J14" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K14" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L14" t="n">
-        <v>1.993907851050025e-07</v>
+        <v>9.026557394875567e-07</v>
       </c>
       <c r="M14" t="n">
-        <v>12.24596902496624</v>
+        <v>12.15055786427058</v>
       </c>
       <c r="N14" t="n">
-        <v>232.1530984531138</v>
+        <v>229.9452553020039</v>
       </c>
       <c r="O14" t="n">
-        <v>15.23657108581566</v>
+        <v>15.16394590144676</v>
       </c>
       <c r="P14" t="n">
-        <v>324.9598810604587</v>
+        <v>324.9715481266679</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -29459,28 +29725,28 @@
         <v>0.0624</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.08882391404901066</v>
+        <v>-0.1009430015830457</v>
       </c>
       <c r="J15" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K15" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L15" t="n">
-        <v>0.002059695854113364</v>
+        <v>0.002709675877662354</v>
       </c>
       <c r="M15" t="n">
-        <v>11.43854928435143</v>
+        <v>11.37250047341512</v>
       </c>
       <c r="N15" t="n">
-        <v>199.6134946168473</v>
+        <v>198.0619955900592</v>
       </c>
       <c r="O15" t="n">
-        <v>14.12846398646531</v>
+        <v>14.07345002442753</v>
       </c>
       <c r="P15" t="n">
-        <v>324.6566004537689</v>
+        <v>324.7918963070613</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -29537,28 +29803,28 @@
         <v>0.0615</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.08780477573806304</v>
+        <v>-0.09658908765859395</v>
       </c>
       <c r="J16" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K16" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L16" t="n">
-        <v>0.002167399614966037</v>
+        <v>0.002674270108892762</v>
       </c>
       <c r="M16" t="n">
-        <v>11.07446206612242</v>
+        <v>11.00519091165169</v>
       </c>
       <c r="N16" t="n">
-        <v>185.3461586051705</v>
+        <v>183.7521132230124</v>
       </c>
       <c r="O16" t="n">
-        <v>13.61418960515721</v>
+        <v>13.55551965890693</v>
       </c>
       <c r="P16" t="n">
-        <v>316.1480067310673</v>
+        <v>316.2460757299245</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -29615,28 +29881,28 @@
         <v>0.0573</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.248782940689526</v>
+        <v>-0.2558755974166386</v>
       </c>
       <c r="J17" t="n">
+        <v>207</v>
+      </c>
+      <c r="K17" t="n">
         <v>205</v>
       </c>
-      <c r="K17" t="n">
-        <v>203</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.01442284354942003</v>
+        <v>0.01555319142590617</v>
       </c>
       <c r="M17" t="n">
-        <v>12.26842696119576</v>
+        <v>12.17779677313824</v>
       </c>
       <c r="N17" t="n">
-        <v>221.0494118457198</v>
+        <v>219.0360374201989</v>
       </c>
       <c r="O17" t="n">
-        <v>14.86773055465157</v>
+        <v>14.79986612845532</v>
       </c>
       <c r="P17" t="n">
-        <v>315.4763546073416</v>
+        <v>315.5556394314281</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -29693,28 +29959,28 @@
         <v>0.0537</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1558955737592066</v>
+        <v>-0.1715661416790262</v>
       </c>
       <c r="J18" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K18" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L18" t="n">
-        <v>0.00582880761277027</v>
+        <v>0.007178564234553542</v>
       </c>
       <c r="M18" t="n">
-        <v>12.10886797676307</v>
+        <v>12.05089135962243</v>
       </c>
       <c r="N18" t="n">
-        <v>216.867174296548</v>
+        <v>215.3665612964786</v>
       </c>
       <c r="O18" t="n">
-        <v>14.72641077440623</v>
+        <v>14.6753726118446</v>
       </c>
       <c r="P18" t="n">
-        <v>311.7917652120954</v>
+        <v>311.9670924613924</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -29771,28 +30037,28 @@
         <v>0.0545</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0413668221616998</v>
+        <v>-0.0564145574207526</v>
       </c>
       <c r="J19" t="n">
+        <v>207</v>
+      </c>
+      <c r="K19" t="n">
         <v>205</v>
       </c>
-      <c r="K19" t="n">
-        <v>203</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.0003622516894778993</v>
+        <v>0.0006863910514283145</v>
       </c>
       <c r="M19" t="n">
-        <v>12.71772216291412</v>
+        <v>12.65043464070426</v>
       </c>
       <c r="N19" t="n">
-        <v>241.7844408234365</v>
+        <v>239.9870128195322</v>
       </c>
       <c r="O19" t="n">
-        <v>15.54941930823902</v>
+        <v>15.49151421971178</v>
       </c>
       <c r="P19" t="n">
-        <v>311.0394487188212</v>
+        <v>311.2095105943055</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -29849,28 +30115,28 @@
         <v>0.0533</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.02898423697874754</v>
+        <v>-0.046686568518708</v>
       </c>
       <c r="J20" t="n">
+        <v>207</v>
+      </c>
+      <c r="K20" t="n">
         <v>205</v>
       </c>
-      <c r="K20" t="n">
-        <v>203</v>
-      </c>
       <c r="L20" t="n">
-        <v>0.0001721682518833756</v>
+        <v>0.0004547266704405528</v>
       </c>
       <c r="M20" t="n">
-        <v>12.7359203298308</v>
+        <v>12.68658165062491</v>
       </c>
       <c r="N20" t="n">
-        <v>253.9386398548058</v>
+        <v>252.2781910733576</v>
       </c>
       <c r="O20" t="n">
-        <v>15.93545229526937</v>
+        <v>15.88326764470578</v>
       </c>
       <c r="P20" t="n">
-        <v>314.2650719224123</v>
+        <v>314.4627377070415</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -29927,28 +30193,28 @@
         <v>0.0487</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1379452654790604</v>
+        <v>-0.1518085983445286</v>
       </c>
       <c r="J21" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K21" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L21" t="n">
-        <v>0.004193576824359835</v>
+        <v>0.005170655199445595</v>
       </c>
       <c r="M21" t="n">
-        <v>12.38026414857078</v>
+        <v>12.31377013526798</v>
       </c>
       <c r="N21" t="n">
-        <v>234.9774476608182</v>
+        <v>233.2166705891728</v>
       </c>
       <c r="O21" t="n">
-        <v>15.32897412290915</v>
+        <v>15.27143315439559</v>
       </c>
       <c r="P21" t="n">
-        <v>322.3455967916458</v>
+        <v>322.5007089317308</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -30005,28 +30271,28 @@
         <v>0.0493</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2468921829571872</v>
+        <v>-0.2639188014993888</v>
       </c>
       <c r="J22" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K22" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0125887013469318</v>
+        <v>0.01461715557555976</v>
       </c>
       <c r="M22" t="n">
-        <v>12.57288421103943</v>
+        <v>12.52120423520055</v>
       </c>
       <c r="N22" t="n">
-        <v>248.6303291382655</v>
+        <v>246.9713805030125</v>
       </c>
       <c r="O22" t="n">
-        <v>15.76801601782119</v>
+        <v>15.71532311163256</v>
       </c>
       <c r="P22" t="n">
-        <v>331.4324066010674</v>
+        <v>331.6228985389616</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -30083,28 +30349,28 @@
         <v>0.0539</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.5052061996406375</v>
+        <v>-0.5442762816294769</v>
       </c>
       <c r="J23" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K23" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L23" t="n">
-        <v>0.05139738597282906</v>
+        <v>0.05948540654100298</v>
       </c>
       <c r="M23" t="n">
-        <v>12.76080377550266</v>
+        <v>12.80850541086991</v>
       </c>
       <c r="N23" t="n">
-        <v>244.9643535895075</v>
+        <v>246.3529481719798</v>
       </c>
       <c r="O23" t="n">
-        <v>15.65133711826269</v>
+        <v>15.69563468522314</v>
       </c>
       <c r="P23" t="n">
-        <v>343.8430672125664</v>
+        <v>344.2801024761901</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -30161,28 +30427,28 @@
         <v>0.0592</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.409952021601897</v>
+        <v>-0.4276739665340758</v>
       </c>
       <c r="J24" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K24" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L24" t="n">
-        <v>0.03468641305536779</v>
+        <v>0.03828567280283712</v>
       </c>
       <c r="M24" t="n">
-        <v>12.62373352889792</v>
+        <v>12.58186474710748</v>
       </c>
       <c r="N24" t="n">
-        <v>243.2189202064694</v>
+        <v>241.6569405240309</v>
       </c>
       <c r="O24" t="n">
-        <v>15.59547755621704</v>
+        <v>15.5453189264174</v>
       </c>
       <c r="P24" t="n">
-        <v>353.6456700872002</v>
+        <v>353.8439311366354</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -30239,28 +30505,28 @@
         <v>0.0698</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3360844052986944</v>
+        <v>-0.3629617682599025</v>
       </c>
       <c r="J25" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K25" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L25" t="n">
-        <v>0.02663285761605461</v>
+        <v>0.03130845305422059</v>
       </c>
       <c r="M25" t="n">
-        <v>11.88431917051859</v>
+        <v>11.88654612271804</v>
       </c>
       <c r="N25" t="n">
-        <v>214.6732348754376</v>
+        <v>214.3924589652105</v>
       </c>
       <c r="O25" t="n">
-        <v>14.65173146339495</v>
+        <v>14.64214666519942</v>
       </c>
       <c r="P25" t="n">
-        <v>365.6531821803387</v>
+        <v>365.9538499256338</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -30317,28 +30583,28 @@
         <v>0.0737</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4657829958574163</v>
+        <v>-0.4884339424334977</v>
       </c>
       <c r="J26" t="n">
+        <v>207</v>
+      </c>
+      <c r="K26" t="n">
         <v>205</v>
       </c>
-      <c r="K26" t="n">
-        <v>203</v>
-      </c>
       <c r="L26" t="n">
-        <v>0.04296115422222635</v>
+        <v>0.04776282337972892</v>
       </c>
       <c r="M26" t="n">
-        <v>12.8040741042534</v>
+        <v>12.77349617207035</v>
       </c>
       <c r="N26" t="n">
-        <v>251.9129607305886</v>
+        <v>250.7243973447691</v>
       </c>
       <c r="O26" t="n">
-        <v>15.87176615032456</v>
+        <v>15.83427918614451</v>
       </c>
       <c r="P26" t="n">
-        <v>359.6771027550967</v>
+        <v>359.9305247769666</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -30395,28 +30661,28 @@
         <v>0.0769</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.5816911301638492</v>
+        <v>-0.6074538269041424</v>
       </c>
       <c r="J27" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K27" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L27" t="n">
-        <v>0.05831065671202695</v>
+        <v>0.06417143655835245</v>
       </c>
       <c r="M27" t="n">
-        <v>13.15319038691482</v>
+        <v>13.12737845367365</v>
       </c>
       <c r="N27" t="n">
-        <v>284.1625687403998</v>
+        <v>283.0381135075546</v>
       </c>
       <c r="O27" t="n">
-        <v>16.85712219628249</v>
+        <v>16.82373660955124</v>
       </c>
       <c r="P27" t="n">
-        <v>353.3205358996029</v>
+        <v>353.6087028612134</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -30473,28 +30739,28 @@
         <v>0.09089999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.6467909466088823</v>
+        <v>-0.6627866038672281</v>
       </c>
       <c r="J28" t="n">
+        <v>207</v>
+      </c>
+      <c r="K28" t="n">
         <v>205</v>
       </c>
-      <c r="K28" t="n">
-        <v>203</v>
-      </c>
       <c r="L28" t="n">
-        <v>0.06124329534285455</v>
+        <v>0.06527400040318576</v>
       </c>
       <c r="M28" t="n">
-        <v>14.28406242565624</v>
+        <v>14.22017513884962</v>
       </c>
       <c r="N28" t="n">
-        <v>333.7438698273434</v>
+        <v>331.1196474343662</v>
       </c>
       <c r="O28" t="n">
-        <v>18.26865812881021</v>
+        <v>18.19669331044424</v>
       </c>
       <c r="P28" t="n">
-        <v>347.7800377673743</v>
+        <v>347.9591703357731</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -30551,28 +30817,28 @@
         <v>0.0786</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.5815772520226484</v>
+        <v>-0.6009179199750421</v>
       </c>
       <c r="J29" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K29" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L29" t="n">
-        <v>0.06057451425260363</v>
+        <v>0.06546657759722585</v>
       </c>
       <c r="M29" t="n">
-        <v>13.39938189780904</v>
+        <v>13.36081367996557</v>
       </c>
       <c r="N29" t="n">
-        <v>278.2870381913415</v>
+        <v>276.5354133606286</v>
       </c>
       <c r="O29" t="n">
-        <v>16.6819374831385</v>
+        <v>16.62935396702556</v>
       </c>
       <c r="P29" t="n">
-        <v>342.661516662301</v>
+        <v>342.8754663842369</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -30629,28 +30895,28 @@
         <v>0.0825</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.6925863502879296</v>
+        <v>-0.722740092183383</v>
       </c>
       <c r="J30" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K30" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L30" t="n">
-        <v>0.07531451238540121</v>
+        <v>0.08248681706145189</v>
       </c>
       <c r="M30" t="n">
-        <v>13.99931064740604</v>
+        <v>14.01261069126833</v>
       </c>
       <c r="N30" t="n">
-        <v>310.8586993940885</v>
+        <v>310.1340814202098</v>
       </c>
       <c r="O30" t="n">
-        <v>17.63118542225929</v>
+        <v>17.61062410649349</v>
       </c>
       <c r="P30" t="n">
-        <v>340.4268261774859</v>
+        <v>340.761414947425</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -30707,28 +30973,28 @@
         <v>0.06809999999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.7803711429296998</v>
+        <v>-0.8041049186504813</v>
       </c>
       <c r="J31" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K31" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="L31" t="n">
-        <v>0.07840527405805942</v>
+        <v>0.08414782526504372</v>
       </c>
       <c r="M31" t="n">
-        <v>15.66714110407027</v>
+        <v>15.63070554644031</v>
       </c>
       <c r="N31" t="n">
-        <v>378.6232866792434</v>
+        <v>376.3244503614938</v>
       </c>
       <c r="O31" t="n">
-        <v>19.45824469676655</v>
+        <v>19.39908375056651</v>
       </c>
       <c r="P31" t="n">
-        <v>338.3575072968034</v>
+        <v>338.6218498696093</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -30785,28 +31051,28 @@
         <v>0.1625</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.673329320474512</v>
+        <v>-0.6894927637963557</v>
       </c>
       <c r="J32" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K32" t="n">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="L32" t="n">
-        <v>0.05470606386905685</v>
+        <v>0.05825759858853696</v>
       </c>
       <c r="M32" t="n">
-        <v>16.62418598555341</v>
+        <v>16.53321596302649</v>
       </c>
       <c r="N32" t="n">
-        <v>410.8797160609668</v>
+        <v>407.4492410040257</v>
       </c>
       <c r="O32" t="n">
-        <v>20.27016813104832</v>
+        <v>20.18537195604841</v>
       </c>
       <c r="P32" t="n">
-        <v>333.4612944848856</v>
+        <v>333.6428092299509</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -30863,28 +31129,28 @@
         <v>0.0556</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.7625438189017202</v>
+        <v>-0.7877199145553294</v>
       </c>
       <c r="J33" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K33" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L33" t="n">
-        <v>0.0625263724842221</v>
+        <v>0.06757874886220494</v>
       </c>
       <c r="M33" t="n">
-        <v>16.67439527180557</v>
+        <v>16.62190907200215</v>
       </c>
       <c r="N33" t="n">
-        <v>455.1872661793098</v>
+        <v>452.14930751753</v>
       </c>
       <c r="O33" t="n">
-        <v>21.33511814308301</v>
+        <v>21.26380275297742</v>
       </c>
       <c r="P33" t="n">
-        <v>331.3158801638567</v>
+        <v>331.5977896880615</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -30941,28 +31207,28 @@
         <v>0.0582</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.241065802262577</v>
+        <v>-1.272700892501593</v>
       </c>
       <c r="J34" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K34" t="n">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="L34" t="n">
-        <v>0.1109368138219012</v>
+        <v>0.1178384281978746</v>
       </c>
       <c r="M34" t="n">
-        <v>20.22516142730645</v>
+        <v>20.1873067931805</v>
       </c>
       <c r="N34" t="n">
-        <v>643.9317244305174</v>
+        <v>639.9119516124355</v>
       </c>
       <c r="O34" t="n">
-        <v>25.37580982807282</v>
+        <v>25.29648101243403</v>
       </c>
       <c r="P34" t="n">
-        <v>331.2564841646334</v>
+        <v>331.6102808146323</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
@@ -31019,28 +31285,28 @@
         <v>0.0295</v>
       </c>
       <c r="I35" t="n">
-        <v>-2.306909833790106</v>
+        <v>-2.321430460450148</v>
       </c>
       <c r="J35" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K35" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="L35" t="n">
-        <v>0.1971840488378529</v>
+        <v>0.2025416021183478</v>
       </c>
       <c r="M35" t="n">
-        <v>26.31466308010825</v>
+        <v>26.12241474784213</v>
       </c>
       <c r="N35" t="n">
-        <v>1123.972061023222</v>
+        <v>1113.354823729454</v>
       </c>
       <c r="O35" t="n">
-        <v>33.52569255098576</v>
+        <v>33.36697204916045</v>
       </c>
       <c r="P35" t="n">
-        <v>336.5399746180988</v>
+        <v>336.7029398072295</v>
       </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
@@ -31097,28 +31363,28 @@
         <v>0.0326</v>
       </c>
       <c r="I36" t="n">
-        <v>-3.590746011265877</v>
+        <v>-3.585109241882963</v>
       </c>
       <c r="J36" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K36" t="n">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="L36" t="n">
-        <v>0.2368162120836074</v>
+        <v>0.2403110369333187</v>
       </c>
       <c r="M36" t="n">
-        <v>37.68539491168868</v>
+        <v>37.31977706861703</v>
       </c>
       <c r="N36" t="n">
-        <v>2171.527596982173</v>
+        <v>2149.214906917998</v>
       </c>
       <c r="O36" t="n">
-        <v>46.59965232683794</v>
+        <v>46.35962582806292</v>
       </c>
       <c r="P36" t="n">
-        <v>346.5093393595106</v>
+        <v>346.4464975216641</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -31179,28 +31445,28 @@
         <v>0.0211</v>
       </c>
       <c r="I37" t="n">
-        <v>-6.440037478408696</v>
+        <v>-6.378746492641435</v>
       </c>
       <c r="J37" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K37" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L37" t="n">
-        <v>0.3606086890086527</v>
+        <v>0.3607748281820276</v>
       </c>
       <c r="M37" t="n">
-        <v>50.23738436904721</v>
+        <v>49.94375357657223</v>
       </c>
       <c r="N37" t="n">
-        <v>3761.038225412707</v>
+        <v>3730.734500723825</v>
       </c>
       <c r="O37" t="n">
-        <v>61.32730407748825</v>
+        <v>61.07973887242663</v>
       </c>
       <c r="P37" t="n">
-        <v>381.2568954606054</v>
+        <v>380.5605005784058</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -31261,28 +31527,28 @@
         <v>0.0218</v>
       </c>
       <c r="I38" t="n">
-        <v>-2.148731335642212</v>
+        <v>-2.214789978462561</v>
       </c>
       <c r="J38" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K38" t="n">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="L38" t="n">
-        <v>0.2412666604197352</v>
+        <v>0.254391274740878</v>
       </c>
       <c r="M38" t="n">
-        <v>22.21619691880679</v>
+        <v>22.25018611398315</v>
       </c>
       <c r="N38" t="n">
-        <v>756.4794107783033</v>
+        <v>758.3699674418995</v>
       </c>
       <c r="O38" t="n">
-        <v>27.50417078877862</v>
+        <v>27.53851788753163</v>
       </c>
       <c r="P38" t="n">
-        <v>334.0827901985942</v>
+        <v>334.8208783865064</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -31343,28 +31609,28 @@
         <v>0.0271</v>
       </c>
       <c r="I39" t="n">
-        <v>-3.277906036221545</v>
+        <v>-2.904731512467444</v>
       </c>
       <c r="J39" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K39" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="L39" t="n">
-        <v>0.2995740840898071</v>
+        <v>0.2632388611086782</v>
       </c>
       <c r="M39" t="n">
-        <v>25.99999098139935</v>
+        <v>25.40561474957701</v>
       </c>
       <c r="N39" t="n">
-        <v>1247.618790068113</v>
+        <v>1167.501438352333</v>
       </c>
       <c r="O39" t="n">
-        <v>35.32164761259182</v>
+        <v>34.16872017433976</v>
       </c>
       <c r="P39" t="n">
-        <v>362.8747161364636</v>
+        <v>358.5602358703126</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -31406,7 +31672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN206"/>
+  <dimension ref="A1:AN208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71830,7 +72096,7 @@
       </c>
       <c r="AM203" t="inlineStr">
         <is>
-          <t>-36.141862553523396,175.43088888947946</t>
+          <t>-36.14164473842933,175.43128433813723</t>
         </is>
       </c>
       <c r="AN203" t="inlineStr">
@@ -72026,11 +72292,7 @@
           <t>-36.14128205227441,175.43034879885627</t>
         </is>
       </c>
-      <c r="AM204" t="inlineStr">
-        <is>
-          <t>-36.142080418005506,175.4304933466905</t>
-        </is>
-      </c>
+      <c r="AM204" t="inlineStr"/>
       <c r="AN204" t="inlineStr">
         <is>
           <t>L8</t>
@@ -72228,11 +72490,7 @@
           <t>-36.141347148162026,175.43023061465408</t>
         </is>
       </c>
-      <c r="AM205" t="inlineStr">
-        <is>
-          <t>-36.14222088527489,175.43023831966212</t>
-        </is>
-      </c>
+      <c r="AM205" t="inlineStr"/>
       <c r="AN205" t="inlineStr">
         <is>
           <t>L8</t>
@@ -72430,14 +72688,414 @@
           <t>-36.141347148162026,175.43023061465408</t>
         </is>
       </c>
-      <c r="AM206" t="inlineStr">
-        <is>
-          <t>-36.14222088527489,175.43023831966212</t>
-        </is>
-      </c>
+      <c r="AM206" t="inlineStr"/>
       <c r="AN206" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:04:54+00:00</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>-36.11621916472841,175.42497538193808</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>-36.11687124836746,175.4245759873923</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>-36.11753445442496,175.424210456724</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>-36.118201578419686,175.42385686603333</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>-36.11894028840538,175.4235682290087</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>-36.11971310318138,175.42326034859778</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>-36.12047381164404,175.42311492862729</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>-36.12119049170776,175.42296774222342</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>-36.12190751152806,175.42282430707996</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>-36.12263460036768,175.42279000642213</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>-36.12336230405979,175.42276243861528</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>-36.12408900277281,175.42272405805667</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>-36.12487296536733,175.42289991094012</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>-36.125654165561194,175.4229007252777</t>
+        </is>
+      </c>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>-36.12639783624975,175.4230223771328</t>
+        </is>
+      </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>-36.12711461877559,175.4231730736361</t>
+        </is>
+      </c>
+      <c r="R207" t="inlineStr">
+        <is>
+          <t>-36.127835220602144,175.42330388433797</t>
+        </is>
+      </c>
+      <c r="S207" t="inlineStr">
+        <is>
+          <t>-36.12853781077888,175.42352828425226</t>
+        </is>
+      </c>
+      <c r="T207" t="inlineStr">
+        <is>
+          <t>-36.129239729139265,175.4237561430201</t>
+        </is>
+      </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>-36.12993378169292,175.42402485422852</t>
+        </is>
+      </c>
+      <c r="V207" t="inlineStr">
+        <is>
+          <t>-36.130633150373335,175.42426589959916</t>
+        </is>
+      </c>
+      <c r="W207" t="inlineStr">
+        <is>
+          <t>-36.131356028445516,175.42438471236636</t>
+        </is>
+      </c>
+      <c r="X207" t="inlineStr">
+        <is>
+          <t>-36.132014714366996,175.42483715572476</t>
+        </is>
+      </c>
+      <c r="Y207" t="inlineStr">
+        <is>
+          <t>-36.13272476634081,175.42513790708904</t>
+        </is>
+      </c>
+      <c r="Z207" t="inlineStr">
+        <is>
+          <t>-36.133420837416274,175.42549353637114</t>
+        </is>
+      </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>-36.13410498753485,175.42582657747184</t>
+        </is>
+      </c>
+      <c r="AB207" t="inlineStr">
+        <is>
+          <t>-36.134748485459546,175.42624319383697</t>
+        </is>
+      </c>
+      <c r="AC207" t="inlineStr">
+        <is>
+          <t>-36.13540540423544,175.42663127175788</t>
+        </is>
+      </c>
+      <c r="AD207" t="inlineStr">
+        <is>
+          <t>-36.13608722612581,175.42696640410787</t>
+        </is>
+      </c>
+      <c r="AE207" t="inlineStr">
+        <is>
+          <t>-36.13672514904271,175.4273948379904</t>
+        </is>
+      </c>
+      <c r="AF207" t="inlineStr">
+        <is>
+          <t>-36.13735475776996,175.42785585613672</t>
+        </is>
+      </c>
+      <c r="AG207" t="inlineStr">
+        <is>
+          <t>-36.13803656663694,175.4282421667303</t>
+        </is>
+      </c>
+      <c r="AH207" t="inlineStr">
+        <is>
+          <t>-36.1387354564959,175.4285961033171</t>
+        </is>
+      </c>
+      <c r="AI207" t="inlineStr">
+        <is>
+          <t>-36.13941635242111,175.4289539583687</t>
+        </is>
+      </c>
+      <c r="AJ207" t="inlineStr">
+        <is>
+          <t>-36.14009537137368,175.4293152120899</t>
+        </is>
+      </c>
+      <c r="AK207" t="inlineStr">
+        <is>
+          <t>-36.140776613438675,175.42967242062517</t>
+        </is>
+      </c>
+      <c r="AL207" t="inlineStr">
+        <is>
+          <t>-36.141347148162026,175.43023061465408</t>
+        </is>
+      </c>
+      <c r="AM207" t="inlineStr">
+        <is>
+          <t>-36.14160970971925,175.43134793320476</t>
+        </is>
+      </c>
+      <c r="AN207" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:06+00:00</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>-36.11620458651084,175.42493101893825</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>-36.116856873002774,175.42453224164953</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>-36.117525524739314,175.4241832826868</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>-36.11819359578064,175.4238325739013</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>-36.118931332881445,175.4235340984511</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>-36.119709687711705,175.42323673258164</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>-36.12047106100015,175.42308513526217</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>-36.121189472944764,175.4229567075433</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>-36.121904098646105,175.42278734056652</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>-36.122631747820634,175.42275910875045</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>-36.12336113248386,175.4227497483818</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>-36.12408708750629,175.4227033120912</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>-36.12487325945434,175.42284249192133</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>-36.12565913138924,175.42286718215698</t>
+        </is>
+      </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>-36.12640288849043,175.42299611633794</t>
+        </is>
+      </c>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>-36.12712033635921,175.42314335436933</t>
+        </is>
+      </c>
+      <c r="R208" t="inlineStr">
+        <is>
+          <t>-36.12784010655723,175.4232784876491</t>
+        </is>
+      </c>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>-36.12854321655924,175.42350018555302</t>
+        </is>
+      </c>
+      <c r="T208" t="inlineStr">
+        <is>
+          <t>-36.12924941803511,175.4237057810826</t>
+        </is>
+      </c>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>-36.12994303405641,175.42397676143034</t>
+        </is>
+      </c>
+      <c r="V208" t="inlineStr">
+        <is>
+          <t>-36.13064179984953,175.42422094056718</t>
+        </is>
+      </c>
+      <c r="W208" t="inlineStr">
+        <is>
+          <t>-36.131360020527445,175.4243639618602</t>
+        </is>
+      </c>
+      <c r="X208" t="inlineStr">
+        <is>
+          <t>-36.13202161746176,175.4248012743837</t>
+        </is>
+      </c>
+      <c r="Y208" t="inlineStr">
+        <is>
+          <t>-36.132735468816655,175.42510430495315</t>
+        </is>
+      </c>
+      <c r="Z208" t="inlineStr">
+        <is>
+          <t>-36.133420837416274,175.42549353637114</t>
+        </is>
+      </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>-36.13410498753485,175.42582657747184</t>
+        </is>
+      </c>
+      <c r="AB208" t="inlineStr">
+        <is>
+          <t>-36.134748485459546,175.42624319383697</t>
+        </is>
+      </c>
+      <c r="AC208" t="inlineStr">
+        <is>
+          <t>-36.13540540423544,175.42663127175788</t>
+        </is>
+      </c>
+      <c r="AD208" t="inlineStr">
+        <is>
+          <t>-36.13608722612581,175.42696640410787</t>
+        </is>
+      </c>
+      <c r="AE208" t="inlineStr">
+        <is>
+          <t>-36.13672514904271,175.4273948379904</t>
+        </is>
+      </c>
+      <c r="AF208" t="inlineStr">
+        <is>
+          <t>-36.13735475776996,175.42785585613672</t>
+        </is>
+      </c>
+      <c r="AG208" t="inlineStr">
+        <is>
+          <t>-36.13803656663694,175.4282421667303</t>
+        </is>
+      </c>
+      <c r="AH208" t="inlineStr">
+        <is>
+          <t>-36.1387354564959,175.4285961033171</t>
+        </is>
+      </c>
+      <c r="AI208" t="inlineStr">
+        <is>
+          <t>-36.13941635242111,175.4289539583687</t>
+        </is>
+      </c>
+      <c r="AJ208" t="inlineStr">
+        <is>
+          <t>-36.14009537137368,175.4293152120899</t>
+        </is>
+      </c>
+      <c r="AK208" t="inlineStr">
+        <is>
+          <t>-36.140776613438675,175.42967242062517</t>
+        </is>
+      </c>
+      <c r="AL208" t="inlineStr">
+        <is>
+          <t>-36.141347148162026,175.43023061465408</t>
+        </is>
+      </c>
+      <c r="AM208" t="inlineStr">
+        <is>
+          <t>-36.141648180555194,175.43127808890782</t>
+        </is>
+      </c>
+      <c r="AN208" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
